--- a/Översikt HÖGSBY.xlsx
+++ b/Översikt HÖGSBY.xlsx
@@ -601,7 +601,7 @@
         <v>46111</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45611</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46111</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>44559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45224</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>46155</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>44867</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>44679</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>45636</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>44866</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>44886</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>45268</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45345</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>45783</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>45982</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45626</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>46184</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>46122</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>44895</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>44853</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>45202</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>45359</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>45230</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>45076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>45352</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>46111</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>45110</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>45268</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>45268</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>46051</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>46184</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>46184</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>46244</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>44617</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>45268</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>44985</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44504</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>44573</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>45883</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>45145</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 23859-2026</t>
+          <t>A 22757-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5129,16 +5129,16 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5153,7 +5153,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5162,49 +5162,49 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 23859-2026 artfynd.xlsx", "A 23859-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 22757-2026 artfynd.xlsx", "A 22757-2026")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 23859-2026 karta.png", "A 23859-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 22757-2026 karta.png", "A 22757-2026")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 23859-2026 georefererad karta.tif", "A 23859-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 22757-2026 georefererad karta.tif", "A 22757-2026")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 23859-2026 FSC-klagomål.docx", "A 23859-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 22757-2026 FSC-klagomål.docx", "A 22757-2026")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 23859-2026 FSC-klagomål mail.docx", "A 23859-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 22757-2026 FSC-klagomål mail.docx", "A 22757-2026")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 23859-2026 tillsynsbegäran.docx", "A 23859-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 22757-2026 tillsynsbegäran.docx", "A 22757-2026")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 23859-2026 tillsynsbegäran mail.docx", "A 23859-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 22757-2026 tillsynsbegäran mail.docx", "A 22757-2026")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24911-2023</t>
+          <t>A 23859-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45085</v>
+        <v>46167</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5234,17 +5234,17 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>1</v>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5267,49 +5267,49 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 24911-2023 artfynd.xlsx", "A 24911-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 23859-2026 artfynd.xlsx", "A 23859-2026")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 24911-2023 karta.png", "A 24911-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 23859-2026 karta.png", "A 23859-2026")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 24911-2023 georefererad karta.tif", "A 24911-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 23859-2026 georefererad karta.tif", "A 23859-2026")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 24911-2023 FSC-klagomål.docx", "A 24911-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 23859-2026 FSC-klagomål.docx", "A 23859-2026")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 24911-2023 FSC-klagomål mail.docx", "A 24911-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 23859-2026 FSC-klagomål mail.docx", "A 23859-2026")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 24911-2023 tillsynsbegäran.docx", "A 24911-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 23859-2026 tillsynsbegäran.docx", "A 23859-2026")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 24911-2023 tillsynsbegäran mail.docx", "A 24911-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 23859-2026 tillsynsbegäran mail.docx", "A 23859-2026")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26145-2026</t>
+          <t>A 24911-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5323,10 +5323,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46181</v>
+        <v>45085</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5339,13 +5339,13 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
         <v>1</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5372,49 +5372,49 @@
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 26145-2026 artfynd.xlsx", "A 26145-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 24911-2023 artfynd.xlsx", "A 24911-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 26145-2026 karta.png", "A 26145-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 24911-2023 karta.png", "A 24911-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 26145-2026 georefererad karta.tif", "A 26145-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 24911-2023 georefererad karta.tif", "A 24911-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 26145-2026 FSC-klagomål.docx", "A 26145-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 24911-2023 FSC-klagomål.docx", "A 24911-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 26145-2026 FSC-klagomål mail.docx", "A 26145-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 24911-2023 FSC-klagomål mail.docx", "A 24911-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 26145-2026 tillsynsbegäran.docx", "A 26145-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 24911-2023 tillsynsbegäran.docx", "A 24911-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 26145-2026 tillsynsbegäran mail.docx", "A 26145-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 24911-2023 tillsynsbegäran mail.docx", "A 24911-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59700-2023</t>
+          <t>A 26145-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45256</v>
+        <v>46181</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -5477,53 +5477,49 @@
         <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 59700-2023 artfynd.xlsx", "A 59700-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 26145-2026 artfynd.xlsx", "A 26145-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 59700-2023 karta.png", "A 59700-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 26145-2026 karta.png", "A 26145-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 59700-2023 georefererad karta.tif", "A 59700-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 26145-2026 georefererad karta.tif", "A 26145-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 59700-2023 FSC-klagomål.docx", "A 59700-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 26145-2026 FSC-klagomål.docx", "A 26145-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 59700-2023 FSC-klagomål mail.docx", "A 59700-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 26145-2026 FSC-klagomål mail.docx", "A 26145-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 59700-2023 tillsynsbegäran.docx", "A 59700-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 26145-2026 tillsynsbegäran.docx", "A 26145-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 59700-2023 tillsynsbegäran mail.docx", "A 59700-2023")</f>
-        <v/>
-      </c>
-      <c r="AE45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/fåglar/A 59700-2023 prioriterade fågelarter.docx", "A 59700-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 26145-2026 tillsynsbegäran mail.docx", "A 26145-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 35072-2023</t>
+          <t>A 59700-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5537,10 +5533,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45145</v>
+        <v>45256</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5553,7 +5549,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -5593,42 +5589,46 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 35072-2023 artfynd.xlsx", "A 35072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 59700-2023 artfynd.xlsx", "A 59700-2023")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 35072-2023 karta.png", "A 35072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 59700-2023 karta.png", "A 59700-2023")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 35072-2023 georefererad karta.tif", "A 35072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 59700-2023 georefererad karta.tif", "A 59700-2023")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 35072-2023 FSC-klagomål.docx", "A 35072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 59700-2023 FSC-klagomål.docx", "A 59700-2023")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 35072-2023 FSC-klagomål mail.docx", "A 35072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 59700-2023 FSC-klagomål mail.docx", "A 59700-2023")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 35072-2023 tillsynsbegäran.docx", "A 35072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 59700-2023 tillsynsbegäran.docx", "A 59700-2023")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 35072-2023 tillsynsbegäran mail.docx", "A 35072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 59700-2023 tillsynsbegäran mail.docx", "A 59700-2023")</f>
+        <v/>
+      </c>
+      <c r="AE46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/fåglar/A 59700-2023 prioriterade fågelarter.docx", "A 59700-2023")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27366-2026</t>
+          <t>A 35072-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46184</v>
+        <v>45145</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -5698,42 +5698,42 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 27366-2026 artfynd.xlsx", "A 27366-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 35072-2023 artfynd.xlsx", "A 35072-2023")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 27366-2026 karta.png", "A 27366-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 35072-2023 karta.png", "A 35072-2023")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 27366-2026 georefererad karta.tif", "A 27366-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 35072-2023 georefererad karta.tif", "A 35072-2023")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 27366-2026 FSC-klagomål.docx", "A 27366-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 35072-2023 FSC-klagomål.docx", "A 35072-2023")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 27366-2026 FSC-klagomål mail.docx", "A 27366-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 35072-2023 FSC-klagomål mail.docx", "A 35072-2023")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 27366-2026 tillsynsbegäran.docx", "A 27366-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 35072-2023 tillsynsbegäran.docx", "A 35072-2023")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 27366-2026 tillsynsbegäran mail.docx", "A 27366-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 35072-2023 tillsynsbegäran mail.docx", "A 35072-2023")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 58792-2022</t>
+          <t>A 27366-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44903</v>
+        <v>46184</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -5807,38 +5807,38 @@
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 58792-2022 artfynd.xlsx", "A 58792-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 27366-2026 artfynd.xlsx", "A 27366-2026")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 58792-2022 karta.png", "A 58792-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 27366-2026 karta.png", "A 27366-2026")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 58792-2022 georefererad karta.tif", "A 58792-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 27366-2026 georefererad karta.tif", "A 27366-2026")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 58792-2022 FSC-klagomål.docx", "A 58792-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 27366-2026 FSC-klagomål.docx", "A 27366-2026")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 58792-2022 FSC-klagomål mail.docx", "A 58792-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 27366-2026 FSC-klagomål mail.docx", "A 27366-2026")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 58792-2022 tillsynsbegäran.docx", "A 58792-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 27366-2026 tillsynsbegäran.docx", "A 27366-2026")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 58792-2022 tillsynsbegäran mail.docx", "A 58792-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 27366-2026 tillsynsbegäran mail.docx", "A 27366-2026")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 28894-2026</t>
+          <t>A 58792-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5852,10 +5852,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46199</v>
+        <v>44903</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>1</v>
@@ -5908,46 +5908,42 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 28894-2026 artfynd.xlsx", "A 28894-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 58792-2022 artfynd.xlsx", "A 58792-2022")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 28894-2026 karta.png", "A 28894-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 58792-2022 karta.png", "A 58792-2022")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 28894-2026 georefererad karta.tif", "A 28894-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 58792-2022 georefererad karta.tif", "A 58792-2022")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 28894-2026 FSC-klagomål.docx", "A 28894-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 58792-2022 FSC-klagomål.docx", "A 58792-2022")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 28894-2026 FSC-klagomål mail.docx", "A 28894-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 58792-2022 FSC-klagomål mail.docx", "A 58792-2022")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 28894-2026 tillsynsbegäran.docx", "A 28894-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 58792-2022 tillsynsbegäran.docx", "A 58792-2022")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 28894-2026 tillsynsbegäran mail.docx", "A 28894-2026")</f>
-        <v/>
-      </c>
-      <c r="AE49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/fåglar/A 28894-2026 prioriterade fågelarter.docx", "A 28894-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 58792-2022 tillsynsbegäran mail.docx", "A 58792-2022")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 17994-2026</t>
+          <t>A 28894-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5961,10 +5957,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46124</v>
+        <v>46199</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5977,10 +5973,10 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>6.3</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -5989,7 +5985,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -6001,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6017,42 +6013,46 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 17994-2026 artfynd.xlsx", "A 17994-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 28894-2026 artfynd.xlsx", "A 28894-2026")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 17994-2026 karta.png", "A 17994-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 28894-2026 karta.png", "A 28894-2026")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 17994-2026 georefererad karta.tif", "A 17994-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 28894-2026 georefererad karta.tif", "A 28894-2026")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 17994-2026 FSC-klagomål.docx", "A 17994-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 28894-2026 FSC-klagomål.docx", "A 28894-2026")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 17994-2026 FSC-klagomål mail.docx", "A 17994-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 28894-2026 FSC-klagomål mail.docx", "A 28894-2026")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 17994-2026 tillsynsbegäran.docx", "A 17994-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 28894-2026 tillsynsbegäran.docx", "A 28894-2026")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 17994-2026 tillsynsbegäran mail.docx", "A 17994-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 28894-2026 tillsynsbegäran mail.docx", "A 28894-2026")</f>
+        <v/>
+      </c>
+      <c r="AE50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/fåglar/A 28894-2026 prioriterade fågelarter.docx", "A 28894-2026")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 19463-2026</t>
+          <t>A 17994-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6066,10 +6066,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46129</v>
+        <v>46124</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6082,20 +6082,20 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
         <v>1</v>
       </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
       <c r="N51" t="n">
         <v>0</v>
       </c>
@@ -6106,10 +6106,10 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6122,42 +6122,42 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 19463-2026 artfynd.xlsx", "A 19463-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 17994-2026 artfynd.xlsx", "A 17994-2026")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 19463-2026 karta.png", "A 19463-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 17994-2026 karta.png", "A 17994-2026")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 19463-2026 georefererad karta.tif", "A 19463-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 17994-2026 georefererad karta.tif", "A 17994-2026")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 19463-2026 FSC-klagomål.docx", "A 19463-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 17994-2026 FSC-klagomål.docx", "A 17994-2026")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 19463-2026 FSC-klagomål mail.docx", "A 19463-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 17994-2026 FSC-klagomål mail.docx", "A 17994-2026")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 19463-2026 tillsynsbegäran.docx", "A 19463-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 17994-2026 tillsynsbegäran.docx", "A 17994-2026")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 19463-2026 tillsynsbegäran mail.docx", "A 19463-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 17994-2026 tillsynsbegäran mail.docx", "A 17994-2026")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 52177-2022</t>
+          <t>A 19463-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44868</v>
+        <v>46129</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
@@ -6196,7 +6196,7 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -6211,7 +6211,7 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -6223,46 +6223,46 @@
         <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 52177-2022 artfynd.xlsx", "A 52177-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 19463-2026 artfynd.xlsx", "A 19463-2026")</f>
         <v/>
       </c>
       <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 52177-2022 karta.png", "A 52177-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 19463-2026 karta.png", "A 19463-2026")</f>
         <v/>
       </c>
       <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 52177-2022 georefererad karta.tif", "A 52177-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 19463-2026 georefererad karta.tif", "A 19463-2026")</f>
         <v/>
       </c>
       <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 52177-2022 FSC-klagomål.docx", "A 52177-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 19463-2026 FSC-klagomål.docx", "A 19463-2026")</f>
         <v/>
       </c>
       <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 52177-2022 FSC-klagomål mail.docx", "A 52177-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 19463-2026 FSC-klagomål mail.docx", "A 19463-2026")</f>
         <v/>
       </c>
       <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 52177-2022 tillsynsbegäran.docx", "A 52177-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 19463-2026 tillsynsbegäran.docx", "A 19463-2026")</f>
         <v/>
       </c>
       <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 52177-2022 tillsynsbegäran mail.docx", "A 52177-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 19463-2026 tillsynsbegäran mail.docx", "A 19463-2026")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 19536-2026</t>
+          <t>A 52177-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46134</v>
+        <v>44868</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>1</v>
@@ -6301,7 +6301,7 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -6316,7 +6316,7 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -6328,50 +6328,46 @@
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="W53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 19536-2026 artfynd.xlsx", "A 19536-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 52177-2022 artfynd.xlsx", "A 52177-2022")</f>
         <v/>
       </c>
       <c r="X53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 19536-2026 karta.png", "A 19536-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 52177-2022 karta.png", "A 52177-2022")</f>
         <v/>
       </c>
       <c r="Y53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 19536-2026 georefererad karta.tif", "A 19536-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 52177-2022 georefererad karta.tif", "A 52177-2022")</f>
         <v/>
       </c>
       <c r="AA53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 19536-2026 FSC-klagomål.docx", "A 19536-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 52177-2022 FSC-klagomål.docx", "A 52177-2022")</f>
         <v/>
       </c>
       <c r="AB53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 19536-2026 FSC-klagomål mail.docx", "A 19536-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 52177-2022 FSC-klagomål mail.docx", "A 52177-2022")</f>
         <v/>
       </c>
       <c r="AC53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 19536-2026 tillsynsbegäran.docx", "A 19536-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 52177-2022 tillsynsbegäran.docx", "A 52177-2022")</f>
         <v/>
       </c>
       <c r="AD53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 19536-2026 tillsynsbegäran mail.docx", "A 19536-2026")</f>
-        <v/>
-      </c>
-      <c r="AE53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/fåglar/A 19536-2026 prioriterade fågelarter.docx", "A 19536-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 52177-2022 tillsynsbegäran mail.docx", "A 52177-2022")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33784-2026</t>
+          <t>A 19536-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6385,10 +6381,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46251</v>
+        <v>46134</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6400,13 +6396,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>8.699999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="J54" t="n">
         <v>1</v>
@@ -6450,42 +6441,42 @@
         </is>
       </c>
       <c r="W54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 33784-2026 artfynd.xlsx", "A 33784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 19536-2026 artfynd.xlsx", "A 19536-2026")</f>
         <v/>
       </c>
       <c r="X54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 33784-2026 karta.png", "A 33784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 19536-2026 karta.png", "A 19536-2026")</f>
         <v/>
       </c>
       <c r="Y54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 33784-2026 georefererad karta.tif", "A 33784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 19536-2026 georefererad karta.tif", "A 19536-2026")</f>
         <v/>
       </c>
       <c r="AA54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 33784-2026 FSC-klagomål.docx", "A 33784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 19536-2026 FSC-klagomål.docx", "A 19536-2026")</f>
         <v/>
       </c>
       <c r="AB54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 33784-2026 FSC-klagomål mail.docx", "A 33784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 19536-2026 FSC-klagomål mail.docx", "A 19536-2026")</f>
         <v/>
       </c>
       <c r="AC54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 33784-2026 tillsynsbegäran.docx", "A 33784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 19536-2026 tillsynsbegäran.docx", "A 19536-2026")</f>
         <v/>
       </c>
       <c r="AD54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 33784-2026 tillsynsbegäran mail.docx", "A 33784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 19536-2026 tillsynsbegäran mail.docx", "A 19536-2026")</f>
         <v/>
       </c>
       <c r="AE54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/fåglar/A 33784-2026 prioriterade fågelarter.docx", "A 33784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/fåglar/A 19536-2026 prioriterade fågelarter.docx", "A 19536-2026")</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 30186-2026</t>
+          <t>A 33784-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6495,14 +6486,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46206</v>
+        <v>46251</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6520,16 +6511,16 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -6544,7 +6535,7 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -6560,42 +6551,46 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 30186-2026 artfynd.xlsx", "A 30186-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 33784-2026 artfynd.xlsx", "A 33784-2026")</f>
         <v/>
       </c>
       <c r="X55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 30186-2026 karta.png", "A 30186-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 33784-2026 karta.png", "A 33784-2026")</f>
         <v/>
       </c>
       <c r="Y55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 30186-2026 georefererad karta.tif", "A 30186-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 33784-2026 georefererad karta.tif", "A 33784-2026")</f>
         <v/>
       </c>
       <c r="AA55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 30186-2026 FSC-klagomål.docx", "A 30186-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 33784-2026 FSC-klagomål.docx", "A 33784-2026")</f>
         <v/>
       </c>
       <c r="AB55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 30186-2026 FSC-klagomål mail.docx", "A 30186-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 33784-2026 FSC-klagomål mail.docx", "A 33784-2026")</f>
         <v/>
       </c>
       <c r="AC55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 30186-2026 tillsynsbegäran.docx", "A 30186-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 33784-2026 tillsynsbegäran.docx", "A 33784-2026")</f>
         <v/>
       </c>
       <c r="AD55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 30186-2026 tillsynsbegäran mail.docx", "A 30186-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 33784-2026 tillsynsbegäran mail.docx", "A 33784-2026")</f>
+        <v/>
+      </c>
+      <c r="AE55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/fåglar/A 33784-2026 prioriterade fågelarter.docx", "A 33784-2026")</f>
         <v/>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30800-2026</t>
+          <t>A 30186-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6605,14 +6600,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46212</v>
+        <v>46206</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6630,17 +6625,17 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
         <v>1</v>
       </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
@@ -6654,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -6670,42 +6665,42 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 30800-2026 artfynd.xlsx", "A 30800-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 30186-2026 artfynd.xlsx", "A 30186-2026")</f>
         <v/>
       </c>
       <c r="X56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 30800-2026 karta.png", "A 30800-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 30186-2026 karta.png", "A 30186-2026")</f>
         <v/>
       </c>
       <c r="Y56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 30800-2026 georefererad karta.tif", "A 30800-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 30186-2026 georefererad karta.tif", "A 30186-2026")</f>
         <v/>
       </c>
       <c r="AA56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 30800-2026 FSC-klagomål.docx", "A 30800-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 30186-2026 FSC-klagomål.docx", "A 30186-2026")</f>
         <v/>
       </c>
       <c r="AB56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 30800-2026 FSC-klagomål mail.docx", "A 30800-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 30186-2026 FSC-klagomål mail.docx", "A 30186-2026")</f>
         <v/>
       </c>
       <c r="AC56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 30800-2026 tillsynsbegäran.docx", "A 30800-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 30186-2026 tillsynsbegäran.docx", "A 30186-2026")</f>
         <v/>
       </c>
       <c r="AD56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 30800-2026 tillsynsbegäran mail.docx", "A 30800-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 30186-2026 tillsynsbegäran mail.docx", "A 30186-2026")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59407-2022</t>
+          <t>A 30800-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6719,10 +6714,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44907</v>
+        <v>46212</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6734,14 +6729,19 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
         <v>1</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -6768,49 +6768,49 @@
         <v>1</v>
       </c>
       <c r="T57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 59407-2022 artfynd.xlsx", "A 59407-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 30800-2026 artfynd.xlsx", "A 30800-2026")</f>
         <v/>
       </c>
       <c r="X57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 59407-2022 karta.png", "A 59407-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 30800-2026 karta.png", "A 30800-2026")</f>
         <v/>
       </c>
       <c r="Y57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 59407-2022 georefererad karta.tif", "A 59407-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 30800-2026 georefererad karta.tif", "A 30800-2026")</f>
         <v/>
       </c>
       <c r="AA57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 59407-2022 FSC-klagomål.docx", "A 59407-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 30800-2026 FSC-klagomål.docx", "A 30800-2026")</f>
         <v/>
       </c>
       <c r="AB57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 59407-2022 FSC-klagomål mail.docx", "A 59407-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 30800-2026 FSC-klagomål mail.docx", "A 30800-2026")</f>
         <v/>
       </c>
       <c r="AC57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 59407-2022 tillsynsbegäran.docx", "A 59407-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 30800-2026 tillsynsbegäran.docx", "A 30800-2026")</f>
         <v/>
       </c>
       <c r="AD57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 59407-2022 tillsynsbegäran mail.docx", "A 59407-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 30800-2026 tillsynsbegäran mail.docx", "A 30800-2026")</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 19519-2025</t>
+          <t>A 59407-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6824,10 +6824,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45770</v>
+        <v>44907</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6840,16 +6840,16 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -6864,7 +6864,7 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -6873,66 +6873,66 @@
         <v>1</v>
       </c>
       <c r="T58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U58" t="n">
         <v>1</v>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 19519-2025 artfynd.xlsx", "A 19519-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 59407-2022 artfynd.xlsx", "A 59407-2022")</f>
         <v/>
       </c>
       <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 19519-2025 karta.png", "A 19519-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 59407-2022 karta.png", "A 59407-2022")</f>
         <v/>
       </c>
       <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 19519-2025 georefererad karta.tif", "A 19519-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 59407-2022 georefererad karta.tif", "A 59407-2022")</f>
         <v/>
       </c>
       <c r="AA58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 19519-2025 FSC-klagomål.docx", "A 19519-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 59407-2022 FSC-klagomål.docx", "A 59407-2022")</f>
         <v/>
       </c>
       <c r="AB58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 19519-2025 FSC-klagomål mail.docx", "A 19519-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 59407-2022 FSC-klagomål mail.docx", "A 59407-2022")</f>
         <v/>
       </c>
       <c r="AC58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 19519-2025 tillsynsbegäran.docx", "A 19519-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 59407-2022 tillsynsbegäran.docx", "A 59407-2022")</f>
         <v/>
       </c>
       <c r="AD58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 19519-2025 tillsynsbegäran mail.docx", "A 19519-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 59407-2022 tillsynsbegäran mail.docx", "A 59407-2022")</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S 352-2023</t>
+          <t>A 19519-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44958</v>
+        <v>45770</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6945,17 +6945,17 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>20.9</v>
+        <v>3.5</v>
       </c>
       <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
         <v>1</v>
       </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
@@ -6969,7 +6969,7 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -6985,50 +6985,42 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="W59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/S 352-2023 artfynd.xlsx", "S 352-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/A 19519-2025 artfynd.xlsx", "A 19519-2025")</f>
         <v/>
       </c>
       <c r="X59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/S 352-2023 karta.png", "S 352-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/A 19519-2025 karta.png", "A 19519-2025")</f>
         <v/>
       </c>
       <c r="Y59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/S 352-2023 georefererad karta.tif", "S 352-2023")</f>
-        <v/>
-      </c>
-      <c r="Z59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/knärot/S 352-2023 karta knärot.png", "S 352-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/A 19519-2025 georefererad karta.tif", "A 19519-2025")</f>
         <v/>
       </c>
       <c r="AA59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/S 352-2023 FSC-klagomål.docx", "S 352-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/A 19519-2025 FSC-klagomål.docx", "A 19519-2025")</f>
         <v/>
       </c>
       <c r="AB59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/S 352-2023 FSC-klagomål mail.docx", "S 352-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/A 19519-2025 FSC-klagomål mail.docx", "A 19519-2025")</f>
         <v/>
       </c>
       <c r="AC59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/S 352-2023 tillsynsbegäran.docx", "S 352-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/A 19519-2025 tillsynsbegäran.docx", "A 19519-2025")</f>
         <v/>
       </c>
       <c r="AD59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/S 352-2023 tillsynsbegäran mail.docx", "S 352-2023")</f>
-        <v/>
-      </c>
-      <c r="AE59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/fåglar/S 352-2023 prioriterade fågelarter.docx", "S 352-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/A 19519-2025 tillsynsbegäran mail.docx", "A 19519-2025")</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S 1694-2022</t>
+          <t>S 352-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7038,14 +7030,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44650</v>
+        <v>44958</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7058,7 +7050,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>20.9</v>
       </c>
       <c r="J60" t="n">
         <v>1</v>
@@ -7094,46 +7086,54 @@
         <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/S 1694-2022 artfynd.xlsx", "S 1694-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/S 352-2023 artfynd.xlsx", "S 352-2023")</f>
         <v/>
       </c>
       <c r="X60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/S 1694-2022 karta.png", "S 1694-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/S 352-2023 karta.png", "S 352-2023")</f>
         <v/>
       </c>
       <c r="Y60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/S 1694-2022 georefererad karta.tif", "S 1694-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/S 352-2023 georefererad karta.tif", "S 352-2023")</f>
+        <v/>
+      </c>
+      <c r="Z60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/knärot/S 352-2023 karta knärot.png", "S 352-2023")</f>
         <v/>
       </c>
       <c r="AA60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/S 1694-2022 FSC-klagomål.docx", "S 1694-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/S 352-2023 FSC-klagomål.docx", "S 352-2023")</f>
         <v/>
       </c>
       <c r="AB60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/S 1694-2022 FSC-klagomål mail.docx", "S 1694-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/S 352-2023 FSC-klagomål mail.docx", "S 352-2023")</f>
         <v/>
       </c>
       <c r="AC60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/S 1694-2022 tillsynsbegäran.docx", "S 1694-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/S 352-2023 tillsynsbegäran.docx", "S 352-2023")</f>
         <v/>
       </c>
       <c r="AD60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/S 1694-2022 tillsynsbegäran mail.docx", "S 1694-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/S 352-2023 tillsynsbegäran mail.docx", "S 352-2023")</f>
+        <v/>
+      </c>
+      <c r="AE60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/fåglar/S 352-2023 prioriterade fågelarter.docx", "S 352-2023")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S 771-2022</t>
+          <t>S 1694-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7143,14 +7143,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44602</v>
+        <v>44650</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7163,13 +7163,13 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>129.1</v>
+        <v>2.2</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -7199,46 +7199,46 @@
         <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/S 771-2022 artfynd.xlsx", "S 771-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/S 1694-2022 artfynd.xlsx", "S 1694-2022")</f>
         <v/>
       </c>
       <c r="X61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/S 771-2022 karta.png", "S 771-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/S 1694-2022 karta.png", "S 1694-2022")</f>
         <v/>
       </c>
       <c r="Y61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/S 771-2022 georefererad karta.tif", "S 771-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/S 1694-2022 georefererad karta.tif", "S 1694-2022")</f>
         <v/>
       </c>
       <c r="AA61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/S 771-2022 FSC-klagomål.docx", "S 771-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/S 1694-2022 FSC-klagomål.docx", "S 1694-2022")</f>
         <v/>
       </c>
       <c r="AB61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/S 771-2022 FSC-klagomål mail.docx", "S 771-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/S 1694-2022 FSC-klagomål mail.docx", "S 1694-2022")</f>
         <v/>
       </c>
       <c r="AC61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/S 771-2022 tillsynsbegäran.docx", "S 771-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/S 1694-2022 tillsynsbegäran.docx", "S 1694-2022")</f>
         <v/>
       </c>
       <c r="AD61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/S 771-2022 tillsynsbegäran mail.docx", "S 771-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/S 1694-2022 tillsynsbegäran mail.docx", "S 1694-2022")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S 1064-2025</t>
+          <t>S 771-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7248,14 +7248,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45749</v>
+        <v>44602</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7267,19 +7267,14 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.5</v>
+        <v>129.1</v>
       </c>
       <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
         <v>1</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -7309,46 +7304,46 @@
         <v>1</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="W62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/S 1064-2025 artfynd.xlsx", "S 1064-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/S 771-2022 artfynd.xlsx", "S 771-2022")</f>
         <v/>
       </c>
       <c r="X62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/S 1064-2025 karta.png", "S 1064-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/S 771-2022 karta.png", "S 771-2022")</f>
         <v/>
       </c>
       <c r="Y62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/S 1064-2025 georefererad karta.tif", "S 1064-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/S 771-2022 georefererad karta.tif", "S 771-2022")</f>
         <v/>
       </c>
       <c r="AA62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/S 1064-2025 FSC-klagomål.docx", "S 1064-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/S 771-2022 FSC-klagomål.docx", "S 771-2022")</f>
         <v/>
       </c>
       <c r="AB62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/S 1064-2025 FSC-klagomål mail.docx", "S 1064-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/S 771-2022 FSC-klagomål mail.docx", "S 771-2022")</f>
         <v/>
       </c>
       <c r="AC62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/S 1064-2025 tillsynsbegäran.docx", "S 1064-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/S 771-2022 tillsynsbegäran.docx", "S 771-2022")</f>
         <v/>
       </c>
       <c r="AD62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/S 1064-2025 tillsynsbegäran mail.docx", "S 1064-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/S 771-2022 tillsynsbegäran mail.docx", "S 771-2022")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S 1216-2025</t>
+          <t>S 1064-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7362,10 +7357,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45761</v>
+        <v>45749</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7377,17 +7372,22 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -7402,7 +7402,7 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -7418,42 +7418,42 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/S 1216-2025 artfynd.xlsx", "S 1216-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/S 1064-2025 artfynd.xlsx", "S 1064-2025")</f>
         <v/>
       </c>
       <c r="X63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/S 1216-2025 karta.png", "S 1216-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/S 1064-2025 karta.png", "S 1064-2025")</f>
         <v/>
       </c>
       <c r="Y63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/S 1216-2025 georefererad karta.tif", "S 1216-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/S 1064-2025 georefererad karta.tif", "S 1064-2025")</f>
         <v/>
       </c>
       <c r="AA63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/S 1216-2025 FSC-klagomål.docx", "S 1216-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/S 1064-2025 FSC-klagomål.docx", "S 1064-2025")</f>
         <v/>
       </c>
       <c r="AB63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/S 1216-2025 FSC-klagomål mail.docx", "S 1216-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/S 1064-2025 FSC-klagomål mail.docx", "S 1064-2025")</f>
         <v/>
       </c>
       <c r="AC63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/S 1216-2025 tillsynsbegäran.docx", "S 1216-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/S 1064-2025 tillsynsbegäran.docx", "S 1064-2025")</f>
         <v/>
       </c>
       <c r="AD63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/S 1216-2025 tillsynsbegäran mail.docx", "S 1216-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/S 1064-2025 tillsynsbegäran mail.docx", "S 1064-2025")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S 380-2023</t>
+          <t>S 1216-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7463,14 +7463,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44958</v>
+        <v>45761</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7483,17 +7483,17 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
         <v>1</v>
       </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
       <c r="M64" t="n">
         <v>0</v>
       </c>
@@ -7507,7 +7507,7 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -7519,46 +7519,46 @@
         <v>1</v>
       </c>
       <c r="U64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="W64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/S 380-2023 artfynd.xlsx", "S 380-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/S 1216-2025 artfynd.xlsx", "S 1216-2025")</f>
         <v/>
       </c>
       <c r="X64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/S 380-2023 karta.png", "S 380-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/S 1216-2025 karta.png", "S 1216-2025")</f>
         <v/>
       </c>
       <c r="Y64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/S 380-2023 georefererad karta.tif", "S 380-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/S 1216-2025 georefererad karta.tif", "S 1216-2025")</f>
         <v/>
       </c>
       <c r="AA64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/S 380-2023 FSC-klagomål.docx", "S 380-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/S 1216-2025 FSC-klagomål.docx", "S 1216-2025")</f>
         <v/>
       </c>
       <c r="AB64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/S 380-2023 FSC-klagomål mail.docx", "S 380-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/S 1216-2025 FSC-klagomål mail.docx", "S 1216-2025")</f>
         <v/>
       </c>
       <c r="AC64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/S 380-2023 tillsynsbegäran.docx", "S 380-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/S 1216-2025 tillsynsbegäran.docx", "S 1216-2025")</f>
         <v/>
       </c>
       <c r="AD64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/S 380-2023 tillsynsbegäran mail.docx", "S 380-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/S 1216-2025 tillsynsbegäran mail.docx", "S 1216-2025")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S 377-2023</t>
+          <t>S 380-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7575,7 +7575,7 @@
         <v>44958</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -7600,7 +7600,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -7612,10 +7612,10 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7624,46 +7624,46 @@
         <v>1</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/S 377-2023 artfynd.xlsx", "S 377-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/S 380-2023 artfynd.xlsx", "S 380-2023")</f>
         <v/>
       </c>
       <c r="X65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/S 377-2023 karta.png", "S 377-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/S 380-2023 karta.png", "S 380-2023")</f>
         <v/>
       </c>
       <c r="Y65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/S 377-2023 georefererad karta.tif", "S 377-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/S 380-2023 georefererad karta.tif", "S 380-2023")</f>
         <v/>
       </c>
       <c r="AA65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/S 377-2023 FSC-klagomål.docx", "S 377-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/S 380-2023 FSC-klagomål.docx", "S 380-2023")</f>
         <v/>
       </c>
       <c r="AB65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/S 377-2023 FSC-klagomål mail.docx", "S 377-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/S 380-2023 FSC-klagomål mail.docx", "S 380-2023")</f>
         <v/>
       </c>
       <c r="AC65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/S 377-2023 tillsynsbegäran.docx", "S 377-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/S 380-2023 tillsynsbegäran.docx", "S 380-2023")</f>
         <v/>
       </c>
       <c r="AD65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/S 377-2023 tillsynsbegäran mail.docx", "S 377-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/S 380-2023 tillsynsbegäran mail.docx", "S 380-2023")</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S 923-2026</t>
+          <t>S 377-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7677,10 +7677,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46111</v>
+        <v>44958</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7693,20 +7693,20 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>65.2</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
         <v>1</v>
       </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
       <c r="N66" t="n">
         <v>0</v>
       </c>
@@ -7717,10 +7717,10 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -7733,59 +7733,59 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="W66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/S 923-2026 artfynd.xlsx", "S 923-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/S 377-2023 artfynd.xlsx", "S 377-2023")</f>
         <v/>
       </c>
       <c r="X66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/S 923-2026 karta.png", "S 923-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/S 377-2023 karta.png", "S 377-2023")</f>
         <v/>
       </c>
       <c r="Y66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/S 923-2026 georefererad karta.tif", "S 923-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/S 377-2023 georefererad karta.tif", "S 377-2023")</f>
         <v/>
       </c>
       <c r="AA66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/S 923-2026 FSC-klagomål.docx", "S 923-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/S 377-2023 FSC-klagomål.docx", "S 377-2023")</f>
         <v/>
       </c>
       <c r="AB66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/S 923-2026 FSC-klagomål mail.docx", "S 923-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/S 377-2023 FSC-klagomål mail.docx", "S 377-2023")</f>
         <v/>
       </c>
       <c r="AC66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/S 923-2026 tillsynsbegäran.docx", "S 923-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/S 377-2023 tillsynsbegäran.docx", "S 377-2023")</f>
         <v/>
       </c>
       <c r="AD66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/S 923-2026 tillsynsbegäran mail.docx", "S 923-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/S 377-2023 tillsynsbegäran mail.docx", "S 377-2023")</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 61740-2021</t>
+          <t>S 923-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44501</v>
+        <v>46111</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7798,14 +7798,14 @@
         </is>
       </c>
       <c r="I67" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
         <v>1</v>
       </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
@@ -7828,20 +7828,52 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
       </c>
-      <c r="V67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="W67">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/artfynd/S 923-2026 artfynd.xlsx", "S 923-2026")</f>
+        <v/>
+      </c>
+      <c r="X67">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor/S 923-2026 karta.png", "S 923-2026")</f>
+        <v/>
+      </c>
+      <c r="Y67">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/kartor_geotiff/S 923-2026 georefererad karta.tif", "S 923-2026")</f>
+        <v/>
+      </c>
+      <c r="AA67">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomål/S 923-2026 FSC-klagomål.docx", "S 923-2026")</f>
+        <v/>
+      </c>
+      <c r="AB67">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/klagomålsmail/S 923-2026 FSC-klagomål mail.docx", "S 923-2026")</f>
+        <v/>
+      </c>
+      <c r="AC67">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsyn/S 923-2026 tillsynsbegäran.docx", "S 923-2026")</f>
+        <v/>
+      </c>
+      <c r="AD67">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0821/tillsynsmail/S 923-2026 tillsynsbegäran mail.docx", "S 923-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 42719-2022</t>
+          <t>A 61740-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7851,14 +7883,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44831</v>
+        <v>44501</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7871,7 +7903,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7914,7 +7946,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 46893-2022</t>
+          <t>A 42719-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7924,14 +7956,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44851</v>
+        <v>44831</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7943,13 +7975,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7992,7 +8019,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 3398-2022</t>
+          <t>A 46893-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -8002,14 +8029,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44585</v>
+        <v>44851</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8021,8 +8048,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -8065,7 +8097,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 50361-2021</t>
+          <t>A 3398-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8079,10 +8111,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44459</v>
+        <v>44585</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8094,13 +8126,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -8143,7 +8170,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 74475-2021</t>
+          <t>A 50361-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8157,10 +8184,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44559</v>
+        <v>44459</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8172,8 +8199,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -8216,7 +8248,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 631-2022</t>
+          <t>A 74475-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8230,10 +8262,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44568</v>
+        <v>44559</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8246,7 +8278,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8289,7 +8321,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7035-2022</t>
+          <t>A 631-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8303,10 +8335,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44603</v>
+        <v>44568</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8319,7 +8351,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8362,7 +8394,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38901-2022</t>
+          <t>A 7035-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8376,10 +8408,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44816</v>
+        <v>44603</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8435,7 +8467,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 74471-2021</t>
+          <t>A 38901-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8449,10 +8481,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44559</v>
+        <v>44816</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8465,7 +8497,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8508,7 +8540,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 7994-2022</t>
+          <t>A 74471-2021</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8522,10 +8554,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44609</v>
+        <v>44559</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8538,7 +8570,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8581,7 +8613,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 2450-2022</t>
+          <t>A 7994-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8595,10 +8627,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44579</v>
+        <v>44609</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8611,7 +8643,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8654,7 +8686,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 18398-2022</t>
+          <t>A 2450-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8668,10 +8700,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44686</v>
+        <v>44579</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8684,7 +8716,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8727,7 +8759,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13149-2022</t>
+          <t>A 18398-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8741,10 +8773,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44644</v>
+        <v>44686</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8757,7 +8789,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8800,7 +8832,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 57372-2021</t>
+          <t>A 13149-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8814,10 +8846,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44482</v>
+        <v>44644</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8830,7 +8862,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8873,7 +8905,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 4890-2022</t>
+          <t>A 57372-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8887,10 +8919,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44593</v>
+        <v>44482</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8903,7 +8935,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8946,7 +8978,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 40105-2022</t>
+          <t>A 4890-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8960,10 +8992,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44818</v>
+        <v>44593</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8976,7 +9008,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6.3</v>
+        <v>3.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -9019,7 +9051,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 73435-2021</t>
+          <t>A 40105-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9033,10 +9065,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44551</v>
+        <v>44818</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9049,7 +9081,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.8</v>
+        <v>6.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -9092,7 +9124,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 71165-2021</t>
+          <t>A 73435-2021</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9106,10 +9138,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44539</v>
+        <v>44551</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9122,7 +9154,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9165,7 +9197,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 51088-2021</t>
+          <t>A 71165-2021</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9179,10 +9211,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44461</v>
+        <v>44539</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9195,7 +9227,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9238,7 +9270,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 23105-2022</t>
+          <t>A 51088-2021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9252,10 +9284,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44719</v>
+        <v>44461</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9268,7 +9300,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9311,7 +9343,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 53808-2022</t>
+          <t>A 23105-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9325,10 +9357,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44880</v>
+        <v>44719</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9341,7 +9373,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9384,7 +9416,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 20128-2022</t>
+          <t>A 53808-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9398,10 +9430,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44698</v>
+        <v>44880</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9413,13 +9445,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9462,7 +9489,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 7703-2022</t>
+          <t>A 20128-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9476,10 +9503,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44607</v>
+        <v>44698</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9491,8 +9518,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9535,7 +9567,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 72059-2021</t>
+          <t>A 7703-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9549,10 +9581,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44542</v>
+        <v>44607</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9565,7 +9597,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>16</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9608,7 +9640,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 72066-2021</t>
+          <t>A 72059-2021</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9625,7 +9657,7 @@
         <v>44542</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9638,7 +9670,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.7</v>
+        <v>16</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9681,7 +9713,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 62274-2021</t>
+          <t>A 72066-2021</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9695,10 +9727,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44503</v>
+        <v>44542</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9711,7 +9743,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9754,7 +9786,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 6540-2022</t>
+          <t>A 62274-2021</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9768,10 +9800,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44601</v>
+        <v>44503</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9784,7 +9816,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9827,7 +9859,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 53242-2022</t>
+          <t>A 6540-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9841,10 +9873,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44876</v>
+        <v>44601</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9857,7 +9889,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9900,7 +9932,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 11768-2022</t>
+          <t>A 53242-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9914,10 +9946,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44634</v>
+        <v>44876</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9930,7 +9962,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9973,7 +10005,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 54941-2022</t>
+          <t>A 11768-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9987,10 +10019,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44886</v>
+        <v>44634</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10002,13 +10034,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -10051,7 +10078,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 18099-2023</t>
+          <t>A 54941-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10065,10 +10092,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45040</v>
+        <v>44886</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10080,8 +10107,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10124,7 +10156,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 56706-2023</t>
+          <t>A 18099-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10138,10 +10170,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45244</v>
+        <v>45040</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10154,7 +10186,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10197,7 +10229,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 14394-2023</t>
+          <t>A 56706-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10211,10 +10243,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45012</v>
+        <v>45244</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10227,7 +10259,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10270,7 +10302,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 57173-2022</t>
+          <t>A 14394-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10284,10 +10316,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44895</v>
+        <v>45012</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10300,7 +10332,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10343,7 +10375,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 30490-2023</t>
+          <t>A 57173-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10357,10 +10389,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45111</v>
+        <v>44895</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10373,7 +10405,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>12.1</v>
+        <v>1.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10416,7 +10448,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 74478-2021</t>
+          <t>A 30490-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10430,10 +10462,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44559</v>
+        <v>45111</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10446,7 +10478,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>12.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10489,7 +10521,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 38797-2024</t>
+          <t>A 74478-2021</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10499,14 +10531,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45547</v>
+        <v>44559</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10518,13 +10550,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10567,7 +10594,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 54483-2022</t>
+          <t>A 38797-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10577,14 +10604,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44882</v>
+        <v>45547</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10596,8 +10623,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10640,7 +10672,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 61955-2023</t>
+          <t>A 54483-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10654,10 +10686,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45266</v>
+        <v>44882</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10670,7 +10702,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10713,7 +10745,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 62385-2023</t>
+          <t>A 61955-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10727,10 +10759,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45268</v>
+        <v>45266</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10743,7 +10775,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10786,7 +10818,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 1582-2024</t>
+          <t>A 62385-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10800,10 +10832,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45306</v>
+        <v>45268</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10815,13 +10847,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>6.7</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10864,7 +10891,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 59281-2022</t>
+          <t>A 1582-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10874,14 +10901,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44904</v>
+        <v>45306</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10895,11 +10922,11 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.2</v>
+        <v>6.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10942,7 +10969,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 13308-2024</t>
+          <t>A 59281-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10952,14 +10979,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45386</v>
+        <v>44904</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10971,8 +10998,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -11015,7 +11047,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 51621-2023</t>
+          <t>A 13308-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -11029,10 +11061,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45222</v>
+        <v>45386</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11044,13 +11076,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -11093,7 +11120,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 37811-2024</t>
+          <t>A 51621-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11103,14 +11130,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45544</v>
+        <v>45222</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11122,8 +11149,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11166,7 +11198,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 15034-2023</t>
+          <t>A 37811-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11176,14 +11208,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45015</v>
+        <v>45544</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11195,13 +11227,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11244,7 +11271,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 38520-2023</t>
+          <t>A 15034-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11258,10 +11285,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45162</v>
+        <v>45015</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11273,8 +11300,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11317,7 +11349,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 12210-2025</t>
+          <t>A 38520-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11331,10 +11363,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45729</v>
+        <v>45162</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11347,7 +11379,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>11.5</v>
+        <v>5.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11390,7 +11422,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 9427-2023</t>
+          <t>A 12210-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11404,10 +11436,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44981</v>
+        <v>45729</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11419,13 +11451,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>8.300000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11468,7 +11495,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 57000-2024</t>
+          <t>A 9427-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11478,14 +11505,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45626</v>
+        <v>44981</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11497,8 +11524,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>5.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11541,7 +11573,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 3982-2023</t>
+          <t>A 57000-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11551,14 +11583,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44950</v>
+        <v>45626</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11571,7 +11603,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11614,7 +11646,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 11478-2023</t>
+          <t>A 3982-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11628,10 +11660,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44991</v>
+        <v>44950</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11644,7 +11676,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11687,7 +11719,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 10413-2023</t>
+          <t>A 11478-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11701,10 +11733,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44987</v>
+        <v>44991</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11717,7 +11749,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11760,7 +11792,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 49338-2022</t>
+          <t>A 10413-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11774,10 +11806,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44861</v>
+        <v>44987</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11790,7 +11822,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11833,7 +11865,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 51619-2023</t>
+          <t>A 49338-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11847,10 +11879,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45222</v>
+        <v>44861</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11862,13 +11894,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11911,7 +11938,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 40155-2023</t>
+          <t>A 51619-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11925,10 +11952,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45168</v>
+        <v>45222</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11942,7 +11969,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I123" t="n">
@@ -11989,7 +12016,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 38596-2024</t>
+          <t>A 40155-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -12003,10 +12030,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45546</v>
+        <v>45168</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12020,11 +12047,11 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -12067,7 +12094,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 10412-2022</t>
+          <t>A 38596-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -12081,10 +12108,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44623</v>
+        <v>45546</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12096,8 +12123,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12140,7 +12172,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 38608-2024</t>
+          <t>A 10412-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12154,10 +12186,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45546</v>
+        <v>44623</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12169,13 +12201,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>9.199999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12218,7 +12245,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 4931-2024</t>
+          <t>A 38608-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12232,10 +12259,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45329</v>
+        <v>45546</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12247,8 +12274,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>0.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12291,7 +12323,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 58753-2022</t>
+          <t>A 4931-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12305,10 +12337,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44903</v>
+        <v>45329</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12321,7 +12353,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12364,7 +12396,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 17185-2022</t>
+          <t>A 58753-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12378,10 +12410,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44677</v>
+        <v>44903</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12394,7 +12426,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12437,7 +12469,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 55703-2023</t>
+          <t>A 17185-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12451,10 +12483,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45239</v>
+        <v>44677</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12467,7 +12499,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12510,7 +12542,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 16014-2025</t>
+          <t>A 55703-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12524,10 +12556,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45749</v>
+        <v>45239</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12540,7 +12572,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12583,7 +12615,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 44437-2023</t>
+          <t>A 16014-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12597,10 +12629,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45189</v>
+        <v>45749</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12613,7 +12645,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12656,7 +12688,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 25861-2023</t>
+          <t>A 44437-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12670,10 +12702,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45090</v>
+        <v>45189</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12686,7 +12718,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12729,7 +12761,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 25876-2023</t>
+          <t>A 25861-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12746,7 +12778,7 @@
         <v>45090</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12759,7 +12791,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12802,7 +12834,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 35723-2024</t>
+          <t>A 25876-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12816,10 +12848,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45532</v>
+        <v>45090</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12832,7 +12864,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12875,7 +12907,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 9700-2023</t>
+          <t>A 35723-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12889,10 +12921,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44984</v>
+        <v>45532</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12905,7 +12937,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12948,7 +12980,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 44436-2023</t>
+          <t>A 9700-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12962,10 +12994,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45189</v>
+        <v>44984</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12978,7 +13010,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -13021,7 +13053,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 36909-2023</t>
+          <t>A 44436-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -13035,10 +13067,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45154</v>
+        <v>45189</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13051,7 +13083,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -13094,7 +13126,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 12757-2023</t>
+          <t>A 36909-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -13108,10 +13140,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45001</v>
+        <v>45154</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13124,7 +13156,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -13167,7 +13199,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 64130-2023</t>
+          <t>A 12757-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -13181,10 +13213,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45279</v>
+        <v>45001</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13197,7 +13229,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -13240,7 +13272,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 32049-2023</t>
+          <t>A 64130-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -13250,14 +13282,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45119</v>
+        <v>45279</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13269,13 +13301,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -13318,7 +13345,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 41706-2023</t>
+          <t>A 32049-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -13328,14 +13355,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45176</v>
+        <v>45119</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13347,8 +13374,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -13391,7 +13423,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 38824-2024</t>
+          <t>A 41706-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -13401,14 +13433,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45547</v>
+        <v>45176</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13420,13 +13452,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>7.7</v>
+        <v>2.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -13469,7 +13496,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 7678-2024</t>
+          <t>A 38824-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -13479,14 +13506,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45348</v>
+        <v>45547</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13498,8 +13525,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>1.6</v>
+        <v>7.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13542,7 +13574,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 28648-2023</t>
+          <t>A 7678-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13552,14 +13584,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45103</v>
+        <v>45348</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13571,13 +13603,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>5.6</v>
+        <v>1.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13620,7 +13647,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 8108-2025</t>
+          <t>A 28648-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13630,14 +13657,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45707</v>
+        <v>45103</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13649,8 +13676,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13693,7 +13725,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 17864-2025</t>
+          <t>A 8108-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13707,10 +13739,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45758</v>
+        <v>45707</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13723,7 +13755,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13766,7 +13798,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 11694-2025</t>
+          <t>A 17864-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13780,10 +13812,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45727</v>
+        <v>45758</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13796,7 +13828,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13839,7 +13871,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 23887-2025</t>
+          <t>A 11694-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13853,10 +13885,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45793</v>
+        <v>45727</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13869,7 +13901,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13912,7 +13944,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 11707-2025</t>
+          <t>A 23887-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13926,10 +13958,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45727</v>
+        <v>45793</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13942,7 +13974,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13985,7 +14017,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 73709-2021</t>
+          <t>A 11707-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13999,10 +14031,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44552</v>
+        <v>45727</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14015,7 +14047,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -14058,7 +14090,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 4821-2026</t>
+          <t>A 73709-2021</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -14072,10 +14104,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46048</v>
+        <v>44552</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14088,7 +14120,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>7.7</v>
+        <v>1.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -14131,7 +14163,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 8116-2025</t>
+          <t>A 4821-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -14145,10 +14177,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45707</v>
+        <v>46048</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14161,7 +14193,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2</v>
+        <v>7.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -14204,7 +14236,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 51724-2025</t>
+          <t>A 8116-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -14218,10 +14250,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45951</v>
+        <v>45707</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14277,7 +14309,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 58679-2022</t>
+          <t>A 51724-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -14291,10 +14323,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44902</v>
+        <v>45951</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14307,7 +14339,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -14350,7 +14382,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 32632-2025</t>
+          <t>A 58679-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -14364,10 +14396,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45838</v>
+        <v>44902</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14380,7 +14412,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -14423,7 +14455,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 22688-2025</t>
+          <t>A 32632-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -14437,10 +14469,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45789</v>
+        <v>45838</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14453,7 +14485,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -14496,7 +14528,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 3548-2024</t>
+          <t>A 22688-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -14510,10 +14542,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45320</v>
+        <v>45789</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14526,7 +14558,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -14569,7 +14601,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 37497-2022</t>
+          <t>A 3548-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14583,10 +14615,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44809</v>
+        <v>45320</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14599,7 +14631,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14642,7 +14674,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 43557-2025</t>
+          <t>A 37497-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14656,10 +14688,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45911</v>
+        <v>44809</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14671,13 +14703,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14720,7 +14747,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 60446-2023</t>
+          <t>A 43557-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14734,10 +14761,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45259</v>
+        <v>45911</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14749,8 +14776,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14793,7 +14825,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 41619-2025</t>
+          <t>A 60446-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14807,10 +14839,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45901</v>
+        <v>45259</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14823,7 +14855,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14866,7 +14898,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 29646-2025</t>
+          <t>A 41619-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14880,10 +14912,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45825</v>
+        <v>45901</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14896,7 +14928,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14939,7 +14971,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 50414-2024</t>
+          <t>A 29646-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14953,10 +14985,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45600</v>
+        <v>45825</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14969,7 +15001,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -15012,7 +15044,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 6819-2025</t>
+          <t>A 50414-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -15026,10 +15058,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45700</v>
+        <v>45600</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15042,7 +15074,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -15085,7 +15117,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 6828-2025</t>
+          <t>A 6819-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -15102,7 +15134,7 @@
         <v>45700</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15115,7 +15147,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -15158,7 +15190,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 56705-2023</t>
+          <t>A 6828-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -15172,10 +15204,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45244</v>
+        <v>45700</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15188,7 +15220,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -15231,7 +15263,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 28650-2023</t>
+          <t>A 56705-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -15245,10 +15277,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45103</v>
+        <v>45244</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15260,13 +15292,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -15309,7 +15336,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 38597-2024</t>
+          <t>A 28650-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -15323,10 +15350,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45546</v>
+        <v>45103</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15344,7 +15371,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -15387,7 +15414,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 63508-2025</t>
+          <t>A 38597-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -15401,10 +15428,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46013</v>
+        <v>45546</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15416,8 +15443,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -15460,7 +15492,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 25223-2022</t>
+          <t>A 63508-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15474,10 +15506,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44729</v>
+        <v>46013</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15490,7 +15522,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -15533,7 +15565,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 4739-2025</t>
+          <t>A 25223-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15547,10 +15579,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45688</v>
+        <v>44729</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15563,7 +15595,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -15606,7 +15638,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 3622-2022</t>
+          <t>A 4739-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15620,10 +15652,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44586</v>
+        <v>45688</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15636,7 +15668,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15679,7 +15711,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 25948-2025</t>
+          <t>A 3622-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15693,10 +15725,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45804</v>
+        <v>44586</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15709,7 +15741,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15752,7 +15784,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 10871-2023</t>
+          <t>A 25948-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15766,10 +15798,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44991</v>
+        <v>45804</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15782,7 +15814,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15825,7 +15857,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 39892-2024</t>
+          <t>A 10871-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15839,10 +15871,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45553</v>
+        <v>44991</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15855,7 +15887,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15898,7 +15930,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 40990-2023</t>
+          <t>A 39892-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15912,10 +15944,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45173</v>
+        <v>45553</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15928,7 +15960,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15971,7 +16003,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 71635-2021</t>
+          <t>A 40990-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15985,10 +16017,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44543</v>
+        <v>45173</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16001,7 +16033,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -16044,7 +16076,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 53108-2023</t>
+          <t>A 71635-2021</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -16058,10 +16090,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45228</v>
+        <v>44543</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16074,7 +16106,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -16117,7 +16149,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 20398-2025</t>
+          <t>A 53108-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16131,10 +16163,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45775</v>
+        <v>45228</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16147,7 +16179,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -16190,7 +16222,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 55902-2024</t>
+          <t>A 20398-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -16204,10 +16236,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45622</v>
+        <v>45775</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16220,7 +16252,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>8.9</v>
+        <v>2.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -16263,7 +16295,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 10405-2025</t>
+          <t>A 55902-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -16277,10 +16309,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45720</v>
+        <v>45622</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16293,7 +16325,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>4</v>
+        <v>8.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -16336,7 +16368,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 11343-2023</t>
+          <t>A 10405-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16350,10 +16382,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44993</v>
+        <v>45720</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16365,13 +16397,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -16414,7 +16441,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 7325-2025</t>
+          <t>A 11343-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16424,14 +16451,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45702</v>
+        <v>44993</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16443,8 +16470,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -16487,7 +16519,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 24292-2022</t>
+          <t>A 7325-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16497,14 +16529,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44725</v>
+        <v>45702</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16517,7 +16549,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -16560,7 +16592,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 50947-2025</t>
+          <t>A 24292-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16574,10 +16606,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45946</v>
+        <v>44725</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16590,7 +16622,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -16633,7 +16665,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 50946-2025</t>
+          <t>A 50947-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16650,7 +16682,7 @@
         <v>45946</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16706,7 +16738,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 50950-2025</t>
+          <t>A 50946-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16723,7 +16755,7 @@
         <v>45946</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16779,7 +16811,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 51720-2025</t>
+          <t>A 50950-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16793,10 +16825,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45950</v>
+        <v>45946</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16809,7 +16841,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>12.8</v>
+        <v>0.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16852,7 +16884,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 21801-2026</t>
+          <t>A 51720-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16866,10 +16898,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46150</v>
+        <v>45950</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16881,13 +16913,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>2</v>
+        <v>12.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16930,7 +16957,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 10704-2022</t>
+          <t>A 21801-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16944,10 +16971,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44625</v>
+        <v>46150</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16959,8 +16986,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -17003,7 +17035,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 10706-2022</t>
+          <t>A 10704-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -17020,7 +17052,7 @@
         <v>44625</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17033,7 +17065,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -17076,7 +17108,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 52575-2025</t>
+          <t>A 10706-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -17090,10 +17122,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45953</v>
+        <v>44625</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17105,13 +17137,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -17154,7 +17181,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 47859-2023</t>
+          <t>A 52575-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -17168,10 +17195,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45204</v>
+        <v>45953</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17183,8 +17210,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -17227,7 +17259,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 52533-2025</t>
+          <t>A 47859-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -17241,10 +17273,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45954</v>
+        <v>45204</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17257,7 +17289,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -17300,7 +17332,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 52545-2025</t>
+          <t>A 52533-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17317,7 +17349,7 @@
         <v>45954</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17330,7 +17362,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -17373,7 +17405,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 36573-2023</t>
+          <t>A 52545-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17387,10 +17419,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45153</v>
+        <v>45954</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17403,7 +17435,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -17446,7 +17478,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 50727-2023</t>
+          <t>A 36573-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -17460,10 +17492,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45217</v>
+        <v>45153</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17476,7 +17508,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -17519,7 +17551,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 14273-2024</t>
+          <t>A 50727-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -17533,10 +17565,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45393</v>
+        <v>45217</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17549,7 +17581,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -17592,7 +17624,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 37320-2022</t>
+          <t>A 14273-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17606,10 +17638,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44809</v>
+        <v>45393</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17622,7 +17654,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -17665,7 +17697,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 22562-2026</t>
+          <t>A 37320-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17675,14 +17707,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46155</v>
+        <v>44809</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17694,13 +17726,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -17743,7 +17770,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 22564-2026</t>
+          <t>A 22562-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17760,7 +17787,7 @@
         <v>46155</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17778,7 +17805,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17821,7 +17848,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 9424-2023</t>
+          <t>A 22564-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17831,14 +17858,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44981</v>
+        <v>46155</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17852,11 +17879,11 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17899,7 +17926,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 17216-2023</t>
+          <t>A 9424-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17913,10 +17940,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45034</v>
+        <v>44981</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17928,8 +17955,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17972,7 +18004,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 6216-2024</t>
+          <t>A 17216-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17986,10 +18018,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45337</v>
+        <v>45034</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18002,7 +18034,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -18045,7 +18077,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 47443-2025</t>
+          <t>A 6216-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -18059,10 +18091,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45930</v>
+        <v>45337</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18074,13 +18106,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -18123,7 +18150,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 58045-2023</t>
+          <t>A 47443-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -18137,10 +18164,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45247</v>
+        <v>45930</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18152,8 +18179,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -18196,7 +18228,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 49485-2022</t>
+          <t>A 58045-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18210,10 +18242,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44861</v>
+        <v>45247</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18226,7 +18258,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -18269,7 +18301,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 56353-2025</t>
+          <t>A 49485-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -18283,10 +18315,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45974</v>
+        <v>44861</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18298,13 +18330,8 @@
           <t>HÖGSBY</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -18347,7 +18374,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 17250-2024</t>
+          <t>A 56353-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -18361,10 +18388,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45414</v>
+        <v>45974</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18376,8 +18403,13 @@
           <t>HÖGSBY</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -18420,7 +18452,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 35047-2023</t>
+          <t>A 17250-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -18434,10 +18466,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45145</v>
+        <v>45414</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18493,7 +18525,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 57168-2025</t>
+          <t>A 35047-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -18507,10 +18539,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45979</v>
+        <v>45145</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18523,7 +18555,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -18566,7 +18598,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 35087-2023</t>
+          <t>A 57168-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -18580,10 +18612,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45145</v>
+        <v>45979</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18596,7 +18628,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -18639,7 +18671,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 27916-2023</t>
+          <t>A 35087-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -18653,10 +18685,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45093</v>
+        <v>45145</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18669,7 +18701,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -18712,7 +18744,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 7438-2023</t>
+          <t>A 27916-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -18726,10 +18758,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44966</v>
+        <v>45093</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18742,7 +18774,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -18785,7 +18817,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 22544-2023</t>
+          <t>A 7438-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18799,10 +18831,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45071</v>
+        <v>44966</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18815,7 +18847,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18858,7 +18890,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 53413-2024</t>
+          <t>A 22544-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18872,10 +18904,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45614</v>
+        <v>45071</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18888,7 +18920,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18931,7 +18963,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 22755-2026</t>
+          <t>A 53413-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18945,10 +18977,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46157</v>
+        <v>45614</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18961,7 +18993,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -19004,7 +19036,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 3549-2024</t>
+          <t>A 22755-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -19018,10 +19050,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45320</v>
+        <v>46157</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19034,7 +19066,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -19077,7 +19109,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 22757-2026</t>
+          <t>A 3549-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19091,10 +19123,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46157</v>
+        <v>45320</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19107,7 +19139,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -19167,7 +19199,7 @@
         <v>45988</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19240,7 +19272,7 @@
         <v>46161</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19313,7 +19345,7 @@
         <v>45105</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19386,7 +19418,7 @@
         <v>45626</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19459,7 +19491,7 @@
         <v>45608</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19532,7 +19564,7 @@
         <v>44496</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19605,7 +19637,7 @@
         <v>44876</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19678,7 +19710,7 @@
         <v>45994</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19756,7 +19788,7 @@
         <v>45274</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19829,7 +19861,7 @@
         <v>46162</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19902,7 +19934,7 @@
         <v>44470</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19980,7 +20012,7 @@
         <v>46167</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20058,7 +20090,7 @@
         <v>46001</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20131,7 +20163,7 @@
         <v>46001</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20204,7 +20236,7 @@
         <v>45999</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20282,7 +20314,7 @@
         <v>45999</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20360,7 +20392,7 @@
         <v>45999</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20438,7 +20470,7 @@
         <v>45999</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20516,7 +20548,7 @@
         <v>45999</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20594,7 +20626,7 @@
         <v>46007</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20667,7 +20699,7 @@
         <v>46009</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20740,7 +20772,7 @@
         <v>46008</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20818,7 +20850,7 @@
         <v>46008</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20896,7 +20928,7 @@
         <v>45190</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20969,7 +21001,7 @@
         <v>46013</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21042,7 +21074,7 @@
         <v>46169</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21115,7 +21147,7 @@
         <v>45391</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21193,7 +21225,7 @@
         <v>45460</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21271,7 +21303,7 @@
         <v>46174</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21349,7 +21381,7 @@
         <v>45058</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21422,7 +21454,7 @@
         <v>46037</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21500,7 +21532,7 @@
         <v>45365</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21573,7 +21605,7 @@
         <v>44613</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21646,7 +21678,7 @@
         <v>46038</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21719,7 +21751,7 @@
         <v>45469</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21797,7 +21829,7 @@
         <v>45348</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21870,7 +21902,7 @@
         <v>45194</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21943,7 +21975,7 @@
         <v>46176</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22016,7 +22048,7 @@
         <v>45348</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22089,7 +22121,7 @@
         <v>46176</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22162,7 +22194,7 @@
         <v>44972</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22235,7 +22267,7 @@
         <v>45113</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22308,7 +22340,7 @@
         <v>44879</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22381,7 +22413,7 @@
         <v>45360</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22459,7 +22491,7 @@
         <v>44907</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22532,7 +22564,7 @@
         <v>45588</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22605,7 +22637,7 @@
         <v>45447</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22678,7 +22710,7 @@
         <v>45126</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22751,7 +22783,7 @@
         <v>46058</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22829,7 +22861,7 @@
         <v>45114</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22902,7 +22934,7 @@
         <v>46059</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22980,7 +23012,7 @@
         <v>46181</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23053,7 +23085,7 @@
         <v>45624</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23126,7 +23158,7 @@
         <v>44601</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23199,7 +23231,7 @@
         <v>46181</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23272,7 +23304,7 @@
         <v>45160</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23345,7 +23377,7 @@
         <v>46184</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23423,7 +23455,7 @@
         <v>46184</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23501,7 +23533,7 @@
         <v>46184</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23579,7 +23611,7 @@
         <v>46184</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23657,7 +23689,7 @@
         <v>45203</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23730,7 +23762,7 @@
         <v>46079</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23803,7 +23835,7 @@
         <v>46184</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23876,7 +23908,7 @@
         <v>46184</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23949,7 +23981,7 @@
         <v>46185</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24027,7 +24059,7 @@
         <v>45175</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24100,7 +24132,7 @@
         <v>46185</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24178,7 +24210,7 @@
         <v>45547</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24256,7 +24288,7 @@
         <v>46188</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24329,7 +24361,7 @@
         <v>44866</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24402,7 +24434,7 @@
         <v>45700</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24475,7 +24507,7 @@
         <v>45700</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24548,7 +24580,7 @@
         <v>46093</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24621,7 +24653,7 @@
         <v>44496</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24694,7 +24726,7 @@
         <v>46191</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24772,7 +24804,7 @@
         <v>45966</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24845,7 +24877,7 @@
         <v>46195</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24923,7 +24955,7 @@
         <v>46196</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25001,7 +25033,7 @@
         <v>46198</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25079,7 +25111,7 @@
         <v>46198</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25157,7 +25189,7 @@
         <v>45743</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25235,7 +25267,7 @@
         <v>46198</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25313,7 +25345,7 @@
         <v>46198</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25391,7 +25423,7 @@
         <v>46197</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25464,7 +25496,7 @@
         <v>46197</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25537,7 +25569,7 @@
         <v>46107</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25610,7 +25642,7 @@
         <v>46198</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25688,7 +25720,7 @@
         <v>46198</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25761,7 +25793,7 @@
         <v>46198</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25834,7 +25866,7 @@
         <v>46198</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25907,7 +25939,7 @@
         <v>46198</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25980,7 +26012,7 @@
         <v>44760</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26053,7 +26085,7 @@
         <v>46111</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26126,7 +26158,7 @@
         <v>46111</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26204,7 +26236,7 @@
         <v>46199</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26277,7 +26309,7 @@
         <v>44879</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26350,7 +26382,7 @@
         <v>46114</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26423,7 +26455,7 @@
         <v>46199</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26496,7 +26528,7 @@
         <v>46199</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26569,7 +26601,7 @@
         <v>44987</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26642,7 +26674,7 @@
         <v>46122</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26715,7 +26747,7 @@
         <v>46122</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26788,7 +26820,7 @@
         <v>45393</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26861,7 +26893,7 @@
         <v>44924</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26934,7 +26966,7 @@
         <v>46202</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27007,7 +27039,7 @@
         <v>45254</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27080,7 +27112,7 @@
         <v>45552</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27153,7 +27185,7 @@
         <v>44999</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27226,7 +27258,7 @@
         <v>46134</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27299,7 +27331,7 @@
         <v>45911</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27377,7 +27409,7 @@
         <v>44981</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27455,7 +27487,7 @@
         <v>45754</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27528,7 +27560,7 @@
         <v>45600</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27601,7 +27633,7 @@
         <v>46013</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27674,7 +27706,7 @@
         <v>45546</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27752,7 +27784,7 @@
         <v>45247</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27825,7 +27857,7 @@
         <v>45288</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27903,7 +27935,7 @@
         <v>46206</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27981,7 +28013,7 @@
         <v>45341</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28054,7 +28086,7 @@
         <v>46206</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28127,7 +28159,7 @@
         <v>44861</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28200,7 +28232,7 @@
         <v>45093</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28273,7 +28305,7 @@
         <v>46251</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28351,7 +28383,7 @@
         <v>45093</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28424,7 +28456,7 @@
         <v>46206</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28502,7 +28534,7 @@
         <v>46206</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28580,7 +28612,7 @@
         <v>46206</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28658,7 +28690,7 @@
         <v>46206</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28736,7 +28768,7 @@
         <v>45183</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28809,7 +28841,7 @@
         <v>45239</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28882,7 +28914,7 @@
         <v>44907</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28955,7 +28987,7 @@
         <v>45608</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29028,7 +29060,7 @@
         <v>45222</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29106,7 +29138,7 @@
         <v>45624</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29179,7 +29211,7 @@
         <v>45544</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29252,7 +29284,7 @@
         <v>44953</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29330,7 +29362,7 @@
         <v>45203</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29403,7 +29435,7 @@
         <v>45203</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29476,7 +29508,7 @@
         <v>44939</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29549,7 +29581,7 @@
         <v>45614</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29622,7 +29654,7 @@
         <v>45581</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29695,7 +29727,7 @@
         <v>45692</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29768,7 +29800,7 @@
         <v>44866</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29841,7 +29873,7 @@
         <v>46266</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29914,7 +29946,7 @@
         <v>46266</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29987,7 +30019,7 @@
         <v>46267</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30060,7 +30092,7 @@
         <v>46267</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30133,7 +30165,7 @@
         <v>46266</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30206,7 +30238,7 @@
         <v>45638</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30279,7 +30311,7 @@
         <v>46269</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30357,7 +30389,7 @@
         <v>46268</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30430,7 +30462,7 @@
         <v>46269</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30508,7 +30540,7 @@
         <v>45307</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30581,7 +30613,7 @@
         <v>46268</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30654,7 +30686,7 @@
         <v>45523</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30727,7 +30759,7 @@
         <v>45782</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30800,7 +30832,7 @@
         <v>46274</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30873,7 +30905,7 @@
         <v>46275</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30951,7 +30983,7 @@
         <v>46275</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31029,7 +31061,7 @@
         <v>46274</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31102,7 +31134,7 @@
         <v>45170</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31175,7 +31207,7 @@
         <v>46237</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31248,7 +31280,7 @@
         <v>45554</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31341,7 +31373,7 @@
         <v>46281</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31414,7 +31446,7 @@
         <v>45797</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31492,7 +31524,7 @@
         <v>46281</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31565,7 +31597,7 @@
         <v>45796</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31638,7 +31670,7 @@
         <v>45847</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31711,7 +31743,7 @@
         <v>45847</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31784,7 +31816,7 @@
         <v>45554</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31857,7 +31889,7 @@
         <v>45882</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31935,7 +31967,7 @@
         <v>44966</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32008,7 +32040,7 @@
         <v>44788</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32086,7 +32118,7 @@
         <v>45524</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32159,7 +32191,7 @@
         <v>44903</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32232,7 +32264,7 @@
         <v>44966</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32305,7 +32337,7 @@
         <v>44966</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32378,7 +32410,7 @@
         <v>45140</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32451,7 +32483,7 @@
         <v>45140</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32524,7 +32556,7 @@
         <v>44592</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32597,7 +32629,7 @@
         <v>45636</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32670,7 +32702,7 @@
         <v>44592</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32743,7 +32775,7 @@
         <v>45835</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32816,7 +32848,7 @@
         <v>44958</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32889,7 +32921,7 @@
         <v>44958</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32962,7 +32994,7 @@
         <v>45938</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33035,7 +33067,7 @@
         <v>46125</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33108,7 +33140,7 @@
         <v>46155</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33186,7 +33218,7 @@
         <v>46155</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33264,7 +33296,7 @@
         <v>46198</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33342,7 +33374,7 @@
         <v>46198</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33420,7 +33452,7 @@
         <v>46198</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33498,7 +33530,7 @@
         <v>46199</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33571,7 +33603,7 @@
         <v>46203</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33644,7 +33676,7 @@
         <v>46251</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>

--- a/Översikt HÖGSBY.xlsx
+++ b/Översikt HÖGSBY.xlsx
@@ -601,7 +601,7 @@
         <v>46111</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45611</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46111</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>44559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45224</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>46155</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>46281</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44867</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44679</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45636</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>44866</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>45345</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>44886</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>45268</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45783</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>44895</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>46122</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45626</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>46184</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>44853</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>45359</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>45202</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>45230</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>45076</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45352</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>46111</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>45268</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>46051</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>45268</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>44617</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>45110</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>46184</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>46184</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>45268</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>44985</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>44504</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>45546</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>46124</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>46129</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>46134</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45883</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45085</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>45547</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>44868</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>44903</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>46157</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>46167</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>44907</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>46181</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>46184</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>45145</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>44573</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>46199</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>46206</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>46251</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>46212</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>45145</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>45770</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>46289</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>45256</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>44650</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>44602</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>44958</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>45749</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>45761</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>44958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>44958</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>46111</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>44501</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>44831</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>44851</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>44585</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44559</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44568</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44603</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44816</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44559</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44609</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44579</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>44686</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>44644</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>44482</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>44593</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44818</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>44551</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>44539</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>44719</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>44880</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>44698</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44607</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44542</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>44542</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>44503</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>44601</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>44876</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>44634</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>45546</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>44876</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>45365</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>44809</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>45393</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44866</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>45268</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>45391</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>45469</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>46013</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>45320</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>45254</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         <v>45796</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>44886</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>45797</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>44902</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>45176</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>45838</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>46037</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45608</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45729</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>46038</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45626</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>46058</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>46059</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>45544</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45775</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>46079</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>46093</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45946</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>45946</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>44991</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45320</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>45743</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>45946</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>45950</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>46107</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>45624</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>45953</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44895</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>46111</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>45266</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>46111</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>45288</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>45954</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>45954</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>45348</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>45626</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>46114</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>45113</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>44496</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>46122</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>46122</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>44991</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>45974</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>45119</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>45608</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>45600</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>45979</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>45614</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>46134</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>45758</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>44999</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>45727</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>45911</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>45754</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>45988</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>45911</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
         <v>45793</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>45951</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>45804</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>45825</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>45901</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>45994</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>45189</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44809</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>45105</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>45999</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>45999</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>45727</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16445,7 +16445,7 @@
         <v>45700</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>45700</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>45707</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>45999</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>46001</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>45999</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>44987</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45999</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>46008</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>46008</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>45552</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17273,7 +17273,7 @@
         <v>46007</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>45228</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>46048</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>46009</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>44861</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>46013</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>45553</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45071</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>46013</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>45600</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44879</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>45247</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>44470</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>45749</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>45244</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>44924</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>45532</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>44861</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44586</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>44981</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>46150</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>45040</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>44904</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45930</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>44939</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>46155</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>46155</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>44866</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>45544</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>46157</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45103</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>46162</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>45111</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45341</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>46161</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>45034</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45093</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45847</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>46167</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>44907</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45847</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>45554</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45624</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>46169</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>45307</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>45114</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>44496</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45460</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45386</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45581</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45058</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>44552</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45393</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>46174</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45546</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45348</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>46176</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>46176</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>44972</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>46181</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>46181</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45360</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>44984</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>46184</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>46184</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>46184</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>46184</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>45175</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45614</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>46185</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>46184</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>45145</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>46184</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>44987</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>46188</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22838,7 +22838,7 @@
         <v>44993</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>46185</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>46191</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>45162</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>45348</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23218,7 +23218,7 @@
         <v>45239</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>45966</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>46195</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>45204</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>46197</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>46197</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>46196</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>46198</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>46198</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>46198</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>46198</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>46198</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>45702</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>46199</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24265,7 +24265,7 @@
         <v>44625</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24338,7 +24338,7 @@
         <v>46198</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44625</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>46199</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>46198</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>46198</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>46198</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>46202</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45882</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>45688</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>45789</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>45707</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>44729</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45203</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45173</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>46206</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>46206</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>45194</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>46206</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>45168</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>46206</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>46251</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>46206</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>46206</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45547</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>45638</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>45090</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>45090</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>45160</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>44677</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>45190</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>45700</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>45700</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>45093</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>44882</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>45247</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>45145</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>45274</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>45154</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>44760</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45259</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45720</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>46266</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>46266</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>46267</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>46267</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>46268</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>46268</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>46266</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>45306</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>46269</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>46269</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>46274</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>44559</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>46274</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>46275</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>46275</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>46237</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>45244</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45547</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>46281</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28803,7 +28803,7 @@
         <v>45329</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28876,7 +28876,7 @@
         <v>46286</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>44861</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>45093</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>46287</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>44543</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>44613</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>44953</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44601</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>45546</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>45447</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>45222</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>45015</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29772,7 +29772,7 @@
         <v>44903</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>45222</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         <v>45217</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>45222</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>44725</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>44981</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>45183</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30298,7 +30298,7 @@
         <v>44950</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         <v>45189</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30444,7 +30444,7 @@
         <v>45012</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30517,7 +30517,7 @@
         <v>45126</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30590,7 +30590,7 @@
         <v>44981</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>45588</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>45692</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>45239</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>45337</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>45001</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>45279</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>45153</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44623</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>44879</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45103</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>44907</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>45203</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         <v>45203</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>44966</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31695,7 +31695,7 @@
         <v>45622</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>45414</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>45523</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>45782</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45170</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45554</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>44592</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>44592</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>44966</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>44788</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32450,7 +32450,7 @@
         <v>45524</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>44903</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>44966</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>44966</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>45140</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>45140</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>45636</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>45835</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>44958</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33107,7 +33107,7 @@
         <v>44958</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>45938</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33253,7 +33253,7 @@
         <v>46125</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>46155</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>46155</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>46198</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>46199</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>46198</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>46198</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>46203</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>46251</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>

--- a/Översikt HÖGSBY.xlsx
+++ b/Översikt HÖGSBY.xlsx
@@ -601,7 +601,7 @@
         <v>46111</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45611</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46111</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>44559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45224</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>46155</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>46281</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44867</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44679</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45636</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>44866</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>45345</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>44886</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>45268</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45783</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>44895</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>46122</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45626</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>46184</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>44853</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>45359</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>45202</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>45230</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>45076</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45352</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>46111</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>45268</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>46051</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>45268</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>44617</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>45110</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>46184</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>46184</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>45268</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>44985</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>44504</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>45546</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>46124</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>46129</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>46134</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45883</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45085</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>45547</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>44868</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>44903</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>46157</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>46167</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>44907</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>46181</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>46184</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>45145</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>44573</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>46199</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>46206</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>46251</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>46212</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>45145</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>45770</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>46289</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>45256</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>44650</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>44602</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>44958</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>45749</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>45761</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>44958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>44958</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>46111</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>44501</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>44831</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>44851</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>44585</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44559</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44568</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44603</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44816</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44559</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44609</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44579</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>44686</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>44644</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>44482</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>44593</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44818</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>44551</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>44539</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>44719</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>44880</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>44698</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44607</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44542</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>44542</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>44503</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>44601</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>44876</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>44634</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>45546</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>44876</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>45365</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>44809</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>45393</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44866</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>45268</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>45391</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>45469</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>46013</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>45320</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>45254</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         <v>45796</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>44886</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>45797</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>44902</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>45176</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>45838</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>46037</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45608</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45729</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>46038</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45626</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>46058</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>46059</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>45544</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45775</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>46079</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>46093</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45946</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>45946</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>44991</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45320</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>45743</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>45946</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>45950</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>46107</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>45624</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>45953</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44895</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>46111</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>45266</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>46111</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>45288</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>45954</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>45954</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>45348</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>45626</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>46114</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>45113</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>44496</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>46122</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>46122</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>44991</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>45974</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>45119</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>45608</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>45600</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>45979</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>45614</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>46134</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>45758</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>44999</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>45727</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>45911</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>45754</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>45988</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>45911</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
         <v>45793</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>45951</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>45804</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>45825</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>45901</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>45994</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>45189</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44809</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>45105</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>45999</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>45999</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>45727</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16445,7 +16445,7 @@
         <v>45700</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>45700</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>45707</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>45999</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>46001</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>45999</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>44987</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45999</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>46008</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>46008</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>45552</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17273,7 +17273,7 @@
         <v>46007</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>45228</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>46048</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>46009</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>44861</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>46013</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>45553</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45071</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>46013</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>45600</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44879</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>45247</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>44470</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>45749</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>45244</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>44924</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>45532</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>44861</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44586</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>44981</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>46150</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>45040</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>44904</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45930</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>44939</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>46155</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>46155</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>44866</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>45544</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>46157</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45103</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>46162</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>45111</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45341</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>46161</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>45034</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45093</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45847</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>46167</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>44907</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45847</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>45554</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45624</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>46169</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>45307</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>45114</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>44496</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45460</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45386</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45581</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45058</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>44552</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45393</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>46174</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45546</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45348</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>46176</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>46176</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>44972</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>46181</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>46181</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45360</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>44984</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>46184</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>46184</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>46184</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>46184</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>45175</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45614</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>46185</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>46184</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>45145</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>46184</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>44987</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>46188</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22838,7 +22838,7 @@
         <v>44993</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>46185</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>46191</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>45162</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>45348</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23218,7 +23218,7 @@
         <v>45239</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>45966</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>46195</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>45204</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>46197</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>46197</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>46196</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>46198</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>46198</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>46198</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>46198</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>46198</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>45702</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>46199</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24265,7 +24265,7 @@
         <v>44625</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24338,7 +24338,7 @@
         <v>46198</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44625</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>46199</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>46198</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>46198</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>46198</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>46202</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45882</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>45688</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>45789</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>45707</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>44729</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45203</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45173</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>46206</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>46206</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>45194</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>46206</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>45168</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>46206</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>46251</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>46206</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>46206</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45547</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>45638</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>45090</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>45090</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>45160</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>44677</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>45190</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>45700</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>45700</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>45093</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>44882</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>45247</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>45145</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>45274</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>45154</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>44760</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45259</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45720</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>46266</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>46266</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>46267</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>46267</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>46268</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>46268</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>46266</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>45306</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>46269</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>46269</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>46274</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>44559</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>46274</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>46275</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>46275</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>46237</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>45244</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45547</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>46281</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28803,7 +28803,7 @@
         <v>45329</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28876,7 +28876,7 @@
         <v>46286</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>44861</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>45093</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>46287</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>44543</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>44613</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>44953</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44601</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>45546</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>45447</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>45222</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>45015</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29772,7 +29772,7 @@
         <v>44903</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>45222</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         <v>45217</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>45222</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>44725</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>44981</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>45183</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30298,7 +30298,7 @@
         <v>44950</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         <v>45189</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30444,7 +30444,7 @@
         <v>45012</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30517,7 +30517,7 @@
         <v>45126</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30590,7 +30590,7 @@
         <v>44981</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>45588</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>45692</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>45239</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>45337</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>45001</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>45279</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>45153</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44623</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>44879</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45103</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>44907</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>45203</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         <v>45203</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>44966</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31695,7 +31695,7 @@
         <v>45622</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>45414</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>45523</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>45782</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45170</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45554</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>44592</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>44592</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>44966</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>44788</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32450,7 +32450,7 @@
         <v>45524</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>44903</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>44966</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>44966</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>45140</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>45140</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>45636</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>45835</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>44958</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33107,7 +33107,7 @@
         <v>44958</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>45938</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33253,7 +33253,7 @@
         <v>46125</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>46155</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>46155</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>46198</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>46199</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>46198</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>46198</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>46203</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>46251</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>

--- a/Översikt HÖGSBY.xlsx
+++ b/Översikt HÖGSBY.xlsx
@@ -601,7 +601,7 @@
         <v>46111</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45611</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46111</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>45224</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>44559</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>46281</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>46155</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44867</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44679</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45636</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>44866</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>44886</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45345</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>45268</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45783</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>46122</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>45626</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>46184</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>44895</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>44853</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>45202</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>45359</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>45230</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>45076</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45352</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>46111</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>46051</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>45110</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>46184</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>46184</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>45268</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45268</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>44617</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>45268</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>44985</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>44504</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>44573</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>45546</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>46129</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>45145</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>46134</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45883</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>46157</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>46167</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>46181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>46184</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>46199</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>45085</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>46206</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>46212</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>45256</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>45145</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>45547</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>44903</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>46289</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>44868</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>46251</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>44907</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45770</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>44958</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44650</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>44602</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>45749</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>45761</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>44958</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>44958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>46111</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>44501</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44831</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>44851</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>44585</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44559</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>44568</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>44603</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>44609</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>44559</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>44579</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>44686</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>44644</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>44482</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>44593</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>44818</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>44551</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>44539</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>44719</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>44880</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>44698</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>44607</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>44542</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>44542</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44503</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>44601</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>44634</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>44876</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>45040</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>44895</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>44886</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>45244</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>45012</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>44559</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>45111</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45266</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>45547</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>45268</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>44882</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45999</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>45015</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>45306</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>45554</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>45222</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>44729</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>44904</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>45688</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>45707</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>45386</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>46007</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>46009</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>46008</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>46008</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>45544</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>46013</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>45838</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>45162</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>44981</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>44950</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>46037</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>45626</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>46038</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>44991</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>44987</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>44861</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>45797</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>45168</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>45222</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45775</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>46058</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>46059</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>44623</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>45546</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>45329</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>45239</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>44677</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>44903</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>45749</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>45189</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>45090</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>45090</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>45946</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>45946</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>45946</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>45950</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>46079</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45532</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45953</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45954</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44984</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>45954</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>45189</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>45154</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>46093</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>45279</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>45001</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>45974</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>45743</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>45979</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>46107</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45119</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>45348</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>46111</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>46111</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>45547</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>45176</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>46114</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>45988</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45103</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>46122</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>46122</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>45994</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>46001</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>45999</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45999</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45999</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>45999</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>44552</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>44902</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>46134</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>45320</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>45911</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45259</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45754</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45700</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45700</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45244</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>46013</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>45103</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>45546</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>45758</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>44586</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>45727</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>45847</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>45793</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>45847</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18469,7 +18469,7 @@
         <v>45727</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>44991</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>46048</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
         <v>45554</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>45707</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18834,7 +18834,7 @@
         <v>45951</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>44809</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>45911</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>45173</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         <v>44543</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45901</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>45825</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>45600</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>45228</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>46013</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>45622</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         <v>45804</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>45720</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>45553</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>44993</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>45702</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>44725</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>44625</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>44625</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>45204</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45153</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>46150</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>45217</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>45393</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>44809</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>46155</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>46155</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>44981</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>45930</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>45034</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>45337</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>46157</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45247</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>44861</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>46161</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>45414</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>45145</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
         <v>46162</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>46167</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>45145</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>45093</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>44966</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45071</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>45614</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>46169</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>45320</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22232,7 +22232,7 @@
         <v>45460</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>46174</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45882</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>46176</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>45105</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45789</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>45626</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>45608</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44496</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>44876</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>46181</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>46181</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>46184</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>46184</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>46184</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>45274</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>46184</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>46184</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>46184</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>46185</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23732,7 +23732,7 @@
         <v>46185</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>46188</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>46191</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>45966</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>45190</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>46195</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>46196</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>46198</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>46198</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>46198</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>46198</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>46197</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>46197</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>46198</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>46198</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>46198</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>46198</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>46198</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>45391</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>46199</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>46199</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>46202</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>46206</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>46206</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45058</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>46206</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>46206</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>46206</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>46206</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>45365</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>44613</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45469</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>45348</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26221,7 +26221,7 @@
         <v>45194</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>45348</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>44972</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>45113</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>44879</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>45360</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26664,7 +26664,7 @@
         <v>44907</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26737,7 +26737,7 @@
         <v>45588</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>45447</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>45126</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>45114</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27029,7 +27029,7 @@
         <v>46266</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>46266</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>46267</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>46267</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>46266</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>46269</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>46268</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>45624</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>44601</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>46269</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>46268</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>45160</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>45203</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27988,7 +27988,7 @@
         <v>46274</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>46275</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>45175</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>46275</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>46274</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>46237</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>46281</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>44866</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>45700</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>45700</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
         <v>44496</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>46287</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>46286</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>44760</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>44879</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>44987</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>45393</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>44924</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29312,7 +29312,7 @@
         <v>46293</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>45254</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>45552</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29531,7 +29531,7 @@
         <v>44999</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>44981</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>46251</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>45600</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>45546</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>45247</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>46297</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30062,7 +30062,7 @@
         <v>45288</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30140,7 +30140,7 @@
         <v>45341</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30213,7 +30213,7 @@
         <v>46176</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30286,7 +30286,7 @@
         <v>44861</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>46297</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>46297</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30515,7 +30515,7 @@
         <v>45093</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>45093</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>45183</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>45239</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>44907</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30880,7 +30880,7 @@
         <v>45608</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>45222</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         <v>45624</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>45544</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>44953</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>45203</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31328,7 +31328,7 @@
         <v>45203</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31401,7 +31401,7 @@
         <v>44939</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45614</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31547,7 +31547,7 @@
         <v>45581</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>45692</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         <v>44866</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>45638</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>45307</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31912,7 +31912,7 @@
         <v>45523</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         <v>45782</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32058,7 +32058,7 @@
         <v>45170</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>44966</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>44788</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>45524</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>44903</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>44966</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>44966</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32574,7 +32574,7 @@
         <v>45140</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32647,7 +32647,7 @@
         <v>45140</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32720,7 +32720,7 @@
         <v>44592</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>45636</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
         <v>44592</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>45835</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33012,7 +33012,7 @@
         <v>44958</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>44958</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>45938</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>46125</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>46155</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>46155</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33460,7 +33460,7 @@
         <v>46198</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>46198</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33616,7 +33616,7 @@
         <v>46198</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33694,7 +33694,7 @@
         <v>46199</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>46203</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>46251</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>46297</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>

--- a/Översikt HÖGSBY.xlsx
+++ b/Översikt HÖGSBY.xlsx
@@ -601,7 +601,7 @@
         <v>46111</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45611</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46111</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>45224</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>44559</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>46281</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>46155</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44867</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44679</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45636</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>44866</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>44886</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45345</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>45268</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45783</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>46122</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>45626</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>46184</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>44895</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>44853</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>45202</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>45359</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>45230</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>45076</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45352</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>46111</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>46051</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>45110</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>46184</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>46184</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>45268</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45268</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>44617</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>45268</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>44985</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>44504</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>44573</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>45546</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>46129</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>45145</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>46134</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45883</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>46157</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>46167</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>46181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>46184</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>46199</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>45085</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>46206</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>46212</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>45256</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>45145</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>45547</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>44903</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>46289</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>44868</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>46251</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>44907</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45770</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>44958</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44650</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>44602</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>45749</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>45761</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>44958</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>44958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>46111</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>44501</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44831</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>44851</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>44585</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44559</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>44568</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>44603</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>44609</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>44559</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>44579</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>44686</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>44644</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>44482</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>44593</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>44818</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>44551</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>44539</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>44719</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>44880</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>44698</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>44607</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>44542</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>44542</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44503</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>44601</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>44634</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>44876</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>45040</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>44895</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>44886</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>45244</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>45012</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>44559</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>45111</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45266</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>45547</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>45268</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>44882</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45999</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>45015</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>45306</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>45554</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>45222</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>44729</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>44904</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>45688</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>45707</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>45386</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>46007</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>46009</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>46008</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>46008</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>45544</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>46013</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>45838</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>45162</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>44981</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>44950</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>46037</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>45626</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>46038</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>44991</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>44987</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>44861</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>45797</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>45168</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>45222</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45775</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>46058</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>46059</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>44623</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>45546</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>45329</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>45239</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>44677</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>44903</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>45749</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>45189</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>45090</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>45090</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>45946</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>45946</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>45946</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>45950</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>46079</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45532</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45953</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45954</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44984</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>45954</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>45189</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>45154</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>46093</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>45279</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>45001</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>45974</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>45743</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>45979</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>46107</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45119</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>45348</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>46111</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>46111</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>45547</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>45176</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>46114</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>45988</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45103</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>46122</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>46122</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>45994</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>46001</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>45999</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45999</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45999</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>45999</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>44552</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>44902</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>46134</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>45320</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>45911</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45259</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45754</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45700</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45700</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45244</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>46013</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>45103</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>45546</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>45758</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>44586</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>45727</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>45847</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>45793</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>45847</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18469,7 +18469,7 @@
         <v>45727</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>44991</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>46048</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
         <v>45554</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>45707</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18834,7 +18834,7 @@
         <v>45951</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>44809</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>45911</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>45173</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         <v>44543</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45901</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>45825</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>45600</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>45228</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>46013</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>45622</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         <v>45804</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>45720</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>45553</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>44993</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>45702</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>44725</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>44625</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>44625</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>45204</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45153</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>46150</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>45217</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>45393</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>44809</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>46155</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>46155</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>44981</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>45930</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>45034</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>45337</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>46157</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45247</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>44861</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>46161</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>45414</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>45145</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
         <v>46162</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>46167</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>45145</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>45093</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>44966</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45071</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>45614</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>46169</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>45320</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22232,7 +22232,7 @@
         <v>45460</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>46174</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45882</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>46176</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>45105</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45789</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>45626</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>45608</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44496</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>44876</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>46181</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>46181</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>46184</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>46184</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>46184</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>45274</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>46184</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>46184</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>46184</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>46185</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23732,7 +23732,7 @@
         <v>46185</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>46188</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>46191</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>45966</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>45190</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>46195</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>46196</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>46198</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>46198</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>46198</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>46198</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>46197</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>46197</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>46198</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>46198</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>46198</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>46198</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>46198</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>45391</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>46199</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>46199</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>46202</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>46206</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>46206</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45058</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>46206</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>46206</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>46206</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>46206</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>45365</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>44613</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45469</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>45348</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26221,7 +26221,7 @@
         <v>45194</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>45348</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>44972</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>45113</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>44879</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>45360</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26664,7 +26664,7 @@
         <v>44907</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26737,7 +26737,7 @@
         <v>45588</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>45447</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>45126</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>45114</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27029,7 +27029,7 @@
         <v>46266</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>46266</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>46267</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>46267</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>46266</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>46269</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>46268</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>45624</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>44601</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>46269</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>46268</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>45160</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>45203</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27988,7 +27988,7 @@
         <v>46274</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>46275</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>45175</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>46275</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>46274</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>46237</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>46281</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>44866</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>45700</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>45700</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
         <v>44496</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>46287</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>46286</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>44760</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>44879</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>44987</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>45393</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>44924</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29312,7 +29312,7 @@
         <v>46293</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>45254</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>45552</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29531,7 +29531,7 @@
         <v>44999</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>44981</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>46251</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>45600</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>45546</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>45247</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>46297</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30062,7 +30062,7 @@
         <v>45288</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30140,7 +30140,7 @@
         <v>45341</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30213,7 +30213,7 @@
         <v>46176</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30286,7 +30286,7 @@
         <v>44861</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>46297</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>46297</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30515,7 +30515,7 @@
         <v>45093</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>45093</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>45183</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>45239</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>44907</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30880,7 +30880,7 @@
         <v>45608</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>45222</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         <v>45624</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>45544</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>44953</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>45203</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31328,7 +31328,7 @@
         <v>45203</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31401,7 +31401,7 @@
         <v>44939</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45614</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31547,7 +31547,7 @@
         <v>45581</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>45692</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         <v>44866</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>45638</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>45307</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31912,7 +31912,7 @@
         <v>45523</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         <v>45782</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32058,7 +32058,7 @@
         <v>45170</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>44966</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>44788</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>45524</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>44903</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>44966</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>44966</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32574,7 +32574,7 @@
         <v>45140</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32647,7 +32647,7 @@
         <v>45140</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32720,7 +32720,7 @@
         <v>44592</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>45636</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
         <v>44592</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>45835</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33012,7 +33012,7 @@
         <v>44958</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>44958</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>45938</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>46125</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>46155</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>46155</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33460,7 +33460,7 @@
         <v>46198</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>46198</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33616,7 +33616,7 @@
         <v>46198</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33694,7 +33694,7 @@
         <v>46199</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>46203</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>46251</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>46297</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>

--- a/Översikt HÖGSBY.xlsx
+++ b/Översikt HÖGSBY.xlsx
@@ -601,7 +601,7 @@
         <v>46111</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45611</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46111</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>44559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45224</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>46281</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>46155</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44867</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44679</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45636</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>44866</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>44886</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45345</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>45268</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45783</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>44895</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>46122</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45626</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>46184</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>44853</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>45230</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>45076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>45359</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>45202</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45352</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>46111</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>45268</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>45110</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>45268</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>45268</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44617</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>46051</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>46184</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>46184</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>46244</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>44985</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>44504</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>44868</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>44903</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>44907</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>45546</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45145</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>44573</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45145</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45770</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>45085</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>45547</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>46129</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>46134</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>45883</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>45256</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>46157</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>46167</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>46181</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>46184</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>46199</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>46206</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>46212</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>46289</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>46251</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>44650</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>44602</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>44958</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>45749</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>45761</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>44958</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>44958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>46111</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>44501</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44831</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>44851</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>44585</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44559</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>44568</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>44603</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>44609</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>44559</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>44579</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>44686</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>44644</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>44880</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>44482</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>44607</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>44593</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>44818</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>44542</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>44542</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>44551</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>44503</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>44539</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>44698</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44601</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>44719</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>44634</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>44876</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>44981</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>44950</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>45189</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>45365</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>44876</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>45040</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>45546</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>45391</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>44904</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>44939</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>44866</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>45544</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>45103</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>45393</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>45012</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>44809</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>45126</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>45111</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>45341</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>44981</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
         <v>45034</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>45093</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>45268</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>45588</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>44866</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>45688</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>44907</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>45789</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>45624</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>45707</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44729</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>45692</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>45469</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>45239</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>45337</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>45320</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>45001</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>45279</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>45307</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>45114</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44496</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>45153</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44623</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>44879</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>45838</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>45254</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>45103</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44886</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45386</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>44907</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>45203</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>45203</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>45581</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>44966</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>45058</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>44552</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>44902</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>45393</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>45176</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>45608</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>45622</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>45546</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>45414</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>45348</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>44972</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>45523</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>45782</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>45360</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>44984</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>45626</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45175</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>45614</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>45145</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44987</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>44993</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>45544</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>45170</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45162</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>45775</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45348</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>45554</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45239</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45204</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45702</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>44625</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>44625</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45797</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45203</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>45173</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>45194</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>44991</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45168</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>45320</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>45624</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45547</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>44895</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>45946</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>45946</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45266</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45288</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45946</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>45638</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>45348</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>45626</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>45090</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>45090</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>45160</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45113</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45950</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44677</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45190</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>44496</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>45700</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>45700</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>45093</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>44882</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>44991</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>45247</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>45953</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45954</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>45954</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>45145</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>45274</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>45154</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>45119</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45608</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44760</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45614</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>44999</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>45259</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45847</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45847</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>45554</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>45974</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45189</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>45105</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>45700</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>45700</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>45306</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>44987</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45552</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45228</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45979</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>44861</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>44559</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45882</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>45071</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>44879</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>45247</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45743</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>45749</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45244</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>45244</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>46107</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44924</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>45532</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>45547</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>44861</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>46111</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>46111</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>45988</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45329</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>44586</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45994</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>46114</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>46122</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>46122</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>44861</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45999</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45999</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>45999</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>46001</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>45999</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>45999</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45093</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23350,7 +23350,7 @@
         <v>44543</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>44613</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>46134</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44953</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45758</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>46008</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>46008</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>44601</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23949,7 +23949,7 @@
         <v>45727</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>45911</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>45754</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>45911</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45793</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
         <v>45951</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>45804</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>45825</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>45901</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>46009</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>44809</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>45447</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>45727</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45707</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>45222</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>45015</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>44903</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>46037</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>46048</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>45222</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>46038</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45217</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>46013</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>45222</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>44725</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>45553</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>46013</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>44981</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>45183</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45600</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>46058</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>46059</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>46079</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>45930</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>46155</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>46155</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>46157</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>46162</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>46093</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>46167</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>46169</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>45460</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>46181</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>46181</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>46184</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>46184</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>46184</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>46184</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>46184</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>46184</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>46188</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>46191</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>45966</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>46197</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>46197</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28064,7 +28064,7 @@
         <v>46196</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>46198</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>46198</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>46198</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28376,7 +28376,7 @@
         <v>46199</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>46198</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>46199</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>46198</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>46198</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>46198</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>46202</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>46206</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>46206</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>46206</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>46206</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>46206</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>46266</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>46266</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>46267</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>46267</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>46268</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>46268</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>46266</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>46269</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>46269</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>46274</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>46274</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>46275</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>46275</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>46237</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>46281</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>46286</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>46287</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>46251</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>46176</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>46297</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30777,7 +30777,7 @@
         <v>46297</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30855,7 +30855,7 @@
         <v>46300</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>46297</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>46293</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>45600</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>46195</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>46174</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>46185</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>46013</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>46150</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>46176</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31610,7 +31610,7 @@
         <v>46198</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31683,7 +31683,7 @@
         <v>44592</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>44592</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31829,7 +31829,7 @@
         <v>44966</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>44788</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>45524</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>44903</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>44966</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>44966</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45140</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>45140</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32418,7 +32418,7 @@
         <v>45636</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32491,7 +32491,7 @@
         <v>45835</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>44958</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>44958</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>45938</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32783,7 +32783,7 @@
         <v>46125</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>46155</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>46155</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33012,7 +33012,7 @@
         <v>46198</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>46199</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>46198</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>46198</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>46203</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>46251</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>46297</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>

--- a/Översikt HÖGSBY.xlsx
+++ b/Översikt HÖGSBY.xlsx
@@ -601,7 +601,7 @@
         <v>46111</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45611</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46111</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>44559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45224</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>46281</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>46155</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44867</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44679</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45636</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>44866</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>44886</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45345</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>45268</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45783</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>44895</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>46122</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45626</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>46184</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>44853</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>45230</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>45076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>45359</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>45202</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45352</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>46111</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>45268</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>45110</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>45268</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>45268</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44617</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>46051</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>46184</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>46184</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>46244</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>44985</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>44504</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>44868</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>44903</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>44907</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>45546</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45145</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>44573</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45145</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45770</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>45085</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>45547</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>46129</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>46134</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>45883</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>45256</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>46157</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>46167</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>46181</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>46184</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>46199</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>46206</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>46212</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>46289</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>46251</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>44650</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>44602</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>44958</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>45749</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>45761</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>44958</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>44958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>46111</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>44501</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44831</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>44851</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>44585</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44559</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>44568</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>44603</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>44609</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>44559</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>44579</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>44686</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>44644</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>44880</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>44482</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>44607</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>44593</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>44818</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>44542</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>44542</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>44551</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>44503</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>44539</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>44698</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44601</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>44719</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>44634</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>44876</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>44981</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>44950</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>45189</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>45365</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>44876</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>45040</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>45546</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>45391</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>44904</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>44939</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>44866</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>45544</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>45103</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>45393</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>45012</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>44809</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>45126</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>45111</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>45341</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>44981</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
         <v>45034</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>45093</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>45268</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>45588</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>44866</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>45688</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>44907</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>45789</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>45624</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>45707</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44729</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>45692</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>45469</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>45239</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>45337</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>45320</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>45001</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>45279</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>45307</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>45114</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44496</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>45153</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44623</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>44879</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>45838</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>45254</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>45103</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44886</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45386</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>44907</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>45203</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>45203</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>45581</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>44966</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>45058</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>44552</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>44902</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>45393</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>45176</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>45608</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>45622</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>45546</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>45414</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>45348</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>44972</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>45523</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>45782</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>45360</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>44984</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>45626</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45175</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>45614</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>45145</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44987</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>44993</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>45544</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>45170</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45162</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>45775</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45348</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>45554</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45239</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45204</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45702</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>44625</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>44625</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45797</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45203</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>45173</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>45194</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>44991</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45168</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>45320</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>45624</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45547</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>44895</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>45946</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>45946</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45266</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45288</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45946</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>45638</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>45348</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>45626</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>45090</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>45090</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>45160</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45113</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45950</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44677</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45190</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>44496</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>45700</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>45700</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>45093</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>44882</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>44991</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>45247</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>45953</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45954</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>45954</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>45145</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>45274</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>45154</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>45119</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45608</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44760</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45614</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>44999</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>45259</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45847</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45847</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>45554</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>45974</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45189</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>45105</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>45700</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>45700</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>45306</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>44987</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45552</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45228</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45979</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>44861</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>44559</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45882</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>45071</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>44879</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>45247</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45743</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>45749</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45244</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>45244</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>46107</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44924</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>45532</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>45547</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>44861</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>46111</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>46111</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>45988</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45329</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>44586</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45994</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>46114</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>46122</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>46122</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>44861</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45999</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45999</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>45999</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>46001</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>45999</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>45999</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45093</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23350,7 +23350,7 @@
         <v>44543</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>44613</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>46134</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44953</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45758</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>46008</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>46008</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>44601</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23949,7 +23949,7 @@
         <v>45727</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>45911</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>45754</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>45911</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45793</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
         <v>45951</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>45804</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>45825</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>45901</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>46009</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>44809</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>45447</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>45727</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45707</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>45222</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>45015</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>44903</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>46037</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>46048</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>45222</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>46038</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45217</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>46013</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>45222</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>44725</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>45553</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>46013</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>44981</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>45183</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45600</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>46058</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>46059</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>46079</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>45930</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>46155</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>46155</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>46157</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>46162</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>46093</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>46167</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>46169</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>45460</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>46181</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>46181</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>46184</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>46184</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>46184</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>46184</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>46184</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>46184</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>46188</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>46191</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>45966</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>46197</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>46197</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28064,7 +28064,7 @@
         <v>46196</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>46198</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>46198</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>46198</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28376,7 +28376,7 @@
         <v>46199</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>46198</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>46199</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>46198</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>46198</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>46198</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>46202</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>46206</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>46206</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>46206</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>46206</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>46206</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>46266</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>46266</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>46267</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>46267</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>46268</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>46268</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>46266</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>46269</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>46269</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>46274</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>46274</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>46275</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>46275</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>46237</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>46281</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>46286</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>46287</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>46251</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>46176</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>46297</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30777,7 +30777,7 @@
         <v>46297</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30855,7 +30855,7 @@
         <v>46300</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>46297</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>46293</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>45600</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>46195</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>46174</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>46185</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>46013</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>46150</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>46176</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31610,7 +31610,7 @@
         <v>46198</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31683,7 +31683,7 @@
         <v>44592</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>44592</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31829,7 +31829,7 @@
         <v>44966</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>44788</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>45524</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>44903</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>44966</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>44966</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45140</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>45140</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32418,7 +32418,7 @@
         <v>45636</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32491,7 +32491,7 @@
         <v>45835</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>44958</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>44958</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>45938</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32783,7 +32783,7 @@
         <v>46125</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>46155</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>46155</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33012,7 +33012,7 @@
         <v>46198</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>46199</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>46198</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>46198</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>46203</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>46251</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>46297</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>

--- a/Översikt HÖGSBY.xlsx
+++ b/Översikt HÖGSBY.xlsx
@@ -601,7 +601,7 @@
         <v>46111</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45611</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46111</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>44559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45224</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>46281</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>44867</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>46199</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>44679</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>45636</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>44866</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>44886</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45268</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45345</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>45783</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>45626</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>46184</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>46122</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44895</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>44853</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>45202</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>45359</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>45230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>45076</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>46307</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>45352</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>46111</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>45110</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>46051</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>45268</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>46184</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>46184</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45268</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44617</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>45268</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>44985</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>44504</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>44573</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>45546</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>45883</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45145</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>46157</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>46167</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>46181</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>46184</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>45085</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>46199</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>45256</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>46129</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>45145</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>46134</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>45547</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>46206</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>46212</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44903</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>44868</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>46289</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>44907</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>46251</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>45770</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44958</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44650</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>44602</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>45749</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>45761</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>44958</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>46111</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>44501</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>44831</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>44851</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>44585</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>44559</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>44568</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>44603</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>44559</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>44609</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>44579</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44686</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>44644</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>44593</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>44818</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>44551</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>44539</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>44719</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>44880</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>44698</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>44607</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>44542</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>44542</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>44503</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>44601</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>44634</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>44876</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>45040</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>44886</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45244</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>44895</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>45012</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>44559</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>45111</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45547</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45266</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>44882</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45268</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45306</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>45015</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>45222</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>44904</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>45386</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45544</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45162</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>44981</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>44950</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>44987</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>45626</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>44861</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>44991</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>45168</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>45222</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>44623</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>44677</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>45239</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>44903</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>45749</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>45189</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>45090</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>45090</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>45532</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>44984</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>45189</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>45154</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>45279</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>45001</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13282,7 +13282,7 @@
         <v>45348</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>45119</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>45707</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>45546</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>45329</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>45758</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>45727</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>45547</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>45176</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45793</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>45727</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>45103</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>46048</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>45707</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>45951</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>44809</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>45911</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>45789</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45838</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45901</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>45825</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>45600</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>44552</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>46013</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>45804</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>44729</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>44902</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>45688</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>45553</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45320</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>45259</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45700</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>45700</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>45244</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>45103</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>44586</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>44991</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>45775</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45173</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44543</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45228</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>45622</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>46155</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>46155</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45946</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>45946</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>45946</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45950</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>45930</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45953</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45954</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>44993</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45954</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45702</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>46157</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>44725</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45974</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>44625</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>44625</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>45204</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45153</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>45979</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>46162</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>45217</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>46167</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45393</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>44809</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>44981</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45034</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45337</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>45988</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45247</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>44861</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>46169</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>45414</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>45994</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45145</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>46001</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>45999</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>45999</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>45999</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45999</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>45145</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>45093</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>45999</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>44966</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45071</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>45614</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>45460</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>45320</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>46009</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>46008</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>46008</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>45105</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>45626</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>45608</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>44496</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>44876</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>45274</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>46037</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>46038</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>45190</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>46181</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>46181</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>46184</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>46058</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>46184</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>46184</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>46059</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>46184</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>45391</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>46184</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>46184</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>46188</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>46079</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45058</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         <v>45365</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>44613</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45469</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>46191</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>45348</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>45966</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>46093</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>45194</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>45348</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>44972</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>45113</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>44879</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>45360</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>44907</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>45588</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>45743</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>45447</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>46196</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>46107</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>46198</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>46198</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>45126</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>46198</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>46198</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>46111</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>46111</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>46197</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>46197</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>46198</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>45114</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24150,7 +24150,7 @@
         <v>46198</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>46198</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24296,7 +24296,7 @@
         <v>46114</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>46199</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>46122</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>46122</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>46199</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45624</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>44601</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>45160</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>46202</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>45203</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>46134</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>45175</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>45911</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>45754</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>46206</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>46013</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>44866</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>45700</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>45700</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>46206</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>46206</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>46206</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>46206</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>44496</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>44760</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>44879</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>44987</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>45393</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>44924</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>46274</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>46275</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>46275</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>46274</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
         <v>45254</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>45552</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>44999</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>46237</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>44981</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>46281</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45546</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>45247</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>45288</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>45341</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>44861</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>45093</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>45093</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>46287</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>45183</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>46286</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>45239</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>44907</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>45608</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>45222</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45624</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>45544</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>44953</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>45203</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>45203</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>44939</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>45614</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45581</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>45692</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>46251</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>44866</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>46297</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>46176</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>46297</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>46297</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>45638</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>45600</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45307</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>46174</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>46293</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>45523</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>45782</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>46195</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>46185</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>45170</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>46176</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>46150</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30241,7 +30241,7 @@
         <v>45554</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>46198</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>46013</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30480,7 +30480,7 @@
         <v>45797</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30558,7 +30558,7 @@
         <v>46300</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30631,7 +30631,7 @@
         <v>46309</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>46266</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>46309</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         <v>46266</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>46266</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>46309</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>46309</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>46309</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>46310</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>46268</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>46267</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>46269</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>46311</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>46267</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>46268</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>46269</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31829,7 +31829,7 @@
         <v>46311</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>46311</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>46311</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>46310</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>45847</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>45847</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v>45554</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>45882</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32418,7 +32418,7 @@
         <v>44966</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32491,7 +32491,7 @@
         <v>44788</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>45524</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32642,7 +32642,7 @@
         <v>44903</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32715,7 +32715,7 @@
         <v>44966</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>44966</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>45140</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>45140</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33007,7 +33007,7 @@
         <v>44592</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>45636</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>44592</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>45835</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>44958</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>44958</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>45938</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>46125</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33591,7 +33591,7 @@
         <v>46155</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>46155</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33747,7 +33747,7 @@
         <v>46198</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>46198</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>46198</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>46199</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>46203</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>46251</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>46297</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>

--- a/Översikt HÖGSBY.xlsx
+++ b/Översikt HÖGSBY.xlsx
@@ -601,7 +601,7 @@
         <v>46111</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45611</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46111</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>44559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45224</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>46281</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>44867</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>46199</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>44679</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>45636</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>44866</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>44886</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45268</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45345</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>45783</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>45626</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>46184</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>46122</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44895</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>44853</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>45202</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>45359</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>45230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>45076</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>46307</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>45352</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>46111</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>45110</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>46051</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>45268</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>46184</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>46184</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45268</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44617</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>45268</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>44985</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>44504</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>44573</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>45546</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>45883</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45145</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>46157</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>46167</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>46181</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>46184</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>45085</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>46199</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>45256</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>46129</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>45145</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>46134</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>45547</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>46206</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>46212</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44903</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>44868</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>46289</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>44907</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>46251</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>45770</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44958</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44650</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>44602</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>45749</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>45761</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>44958</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>46111</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>44501</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>44831</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>44851</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>44585</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>44559</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>44568</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>44603</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>44559</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>44609</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>44579</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44686</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>44644</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>44593</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>44818</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>44551</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>44539</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>44719</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>44880</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>44698</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>44607</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>44542</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>44542</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>44503</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>44601</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>44634</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>44876</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>45040</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>44886</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45244</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>44895</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>45012</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>44559</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>45111</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45547</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45266</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>44882</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45268</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45306</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>45015</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>45222</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>44904</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>45386</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45544</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45162</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>44981</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>44950</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>44987</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>45626</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>44861</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>44991</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>45168</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>45222</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>44623</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>44677</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>45239</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>44903</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>45749</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>45189</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>45090</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>45090</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>45532</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>44984</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>45189</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>45154</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>45279</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>45001</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13282,7 +13282,7 @@
         <v>45348</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>45119</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>45707</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>45546</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>45329</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>45758</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>45727</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>45547</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>45176</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45793</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>45727</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>45103</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>46048</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>45707</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>45951</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>44809</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>45911</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>45789</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45838</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45901</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>45825</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>45600</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>44552</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>46013</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>45804</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>44729</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>44902</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>45688</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>45553</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45320</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>45259</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45700</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>45700</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>45244</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>45103</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>44586</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>44991</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>45775</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45173</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44543</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45228</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>45622</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>46155</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>46155</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45946</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>45946</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>45946</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45950</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>45930</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45953</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45954</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>44993</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45954</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45702</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>46157</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>44725</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45974</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>44625</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>44625</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>45204</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45153</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>45979</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>46162</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>45217</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>46167</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45393</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>44809</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>44981</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45034</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45337</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>45988</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45247</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>44861</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>46169</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>45414</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>45994</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45145</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>46001</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>45999</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>45999</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>45999</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45999</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>45145</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>45093</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>45999</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>44966</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45071</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>45614</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>45460</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>45320</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>46009</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>46008</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>46008</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>45105</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>45626</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>45608</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>44496</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>44876</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>45274</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>46037</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>46038</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>45190</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>46181</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>46181</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>46184</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>46058</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>46184</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>46184</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>46059</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>46184</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>45391</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>46184</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>46184</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>46188</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>46079</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45058</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         <v>45365</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>44613</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45469</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>46191</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>45348</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>45966</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>46093</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>45194</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>45348</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>44972</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>45113</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>44879</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>45360</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>44907</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>45588</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>45743</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>45447</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>46196</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>46107</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>46198</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>46198</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>45126</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>46198</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>46198</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>46111</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>46111</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>46197</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>46197</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>46198</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>45114</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24150,7 +24150,7 @@
         <v>46198</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>46198</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24296,7 +24296,7 @@
         <v>46114</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>46199</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>46122</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>46122</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>46199</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45624</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>44601</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>45160</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>46202</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>45203</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>46134</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>45175</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>45911</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>45754</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>46206</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>46013</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>44866</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>45700</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>45700</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>46206</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>46206</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>46206</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>46206</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>44496</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>44760</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>44879</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>44987</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>45393</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>44924</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>46274</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>46275</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>46275</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>46274</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
         <v>45254</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>45552</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>44999</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>46237</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>44981</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>46281</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45546</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>45247</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>45288</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>45341</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>44861</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>45093</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>45093</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>46287</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>45183</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>46286</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>45239</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>44907</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>45608</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>45222</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45624</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>45544</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>44953</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>45203</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>45203</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>44939</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>45614</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45581</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>45692</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>46251</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>44866</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>46297</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>46176</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>46297</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>46297</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>45638</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>45600</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45307</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>46174</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>46293</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>45523</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>45782</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>46195</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>46185</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>45170</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>46176</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>46150</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30241,7 +30241,7 @@
         <v>45554</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>46198</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>46013</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30480,7 +30480,7 @@
         <v>45797</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30558,7 +30558,7 @@
         <v>46300</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30631,7 +30631,7 @@
         <v>46309</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>46266</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>46309</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         <v>46266</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>46266</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>46309</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>46309</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>46309</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>46310</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>46268</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>46267</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>46269</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>46311</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>46267</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>46268</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>46269</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31829,7 +31829,7 @@
         <v>46311</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>46311</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>46311</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>46310</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>45847</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>45847</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v>45554</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>45882</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32418,7 +32418,7 @@
         <v>44966</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32491,7 +32491,7 @@
         <v>44788</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>45524</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32642,7 +32642,7 @@
         <v>44903</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32715,7 +32715,7 @@
         <v>44966</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>44966</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>45140</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>45140</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33007,7 +33007,7 @@
         <v>44592</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>45636</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>44592</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>45835</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>44958</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>44958</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>45938</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>46125</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33591,7 +33591,7 @@
         <v>46155</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>46155</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33747,7 +33747,7 @@
         <v>46198</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>46198</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>46198</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>46199</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>46203</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>46251</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>46297</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>

--- a/Översikt HÖGSBY.xlsx
+++ b/Översikt HÖGSBY.xlsx
@@ -601,7 +601,7 @@
         <v>46111</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45611</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46111</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>44559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45224</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>46281</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>44867</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>46199</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>44679</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>45636</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>44866</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>45268</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>45345</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44886</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>45783</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>45626</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>44895</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>46184</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45982</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>46122</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>44853</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>45230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>46307</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>45359</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>45202</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>45352</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>46111</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>45268</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>46184</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>46184</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>45268</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46244</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>46051</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>45268</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>44617</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>45110</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>44985</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>44504</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>45256</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>46167</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>46181</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>46184</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>46199</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>46206</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>46212</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>46289</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>46251</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>46129</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>46134</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45883</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>45546</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>46157</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>45085</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>45547</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>44868</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>44903</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>44907</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>45145</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>44573</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>45145</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>45770</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44650</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>44602</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>44958</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>45749</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>45761</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>44958</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>46111</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>44501</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>44831</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>44851</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>44585</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>44559</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>44568</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>44603</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>44609</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>44559</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>44579</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44686</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>44644</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>44593</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>44818</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>44551</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>44539</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>44719</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>44880</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>44698</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>44607</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>44542</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>44542</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>44503</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>44601</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>44876</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>44634</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>44543</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>44613</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>44953</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>45838</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>44601</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>45546</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>45447</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>46162</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45222</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>45015</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>44903</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>46167</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45775</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>45222</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>45217</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>45365</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45222</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>44725</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>46169</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>44876</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>44981</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>45183</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>45460</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>45391</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>44950</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>45189</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>45393</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>45946</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>45946</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>44809</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>46181</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>45946</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>45950</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>46181</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>45953</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>46184</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>46184</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>45954</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>46184</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>46184</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>45954</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>46184</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>45012</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>46184</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45126</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>46188</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>45268</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>44866</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>44981</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>46191</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>45588</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45966</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>45692</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>46197</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>46197</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>46196</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>45974</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>45239</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>45337</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>46198</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>46198</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>46198</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>46199</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>45001</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>46198</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>46199</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>46198</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>45279</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>46198</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>46198</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>46202</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>45153</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>45979</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>44623</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>45469</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>44879</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>45103</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>44907</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>45203</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>45203</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44966</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>46206</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>46206</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>46206</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>46206</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>46206</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>45988</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>45994</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>45622</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>45320</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>45414</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>45999</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45999</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>45999</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>46001</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>45999</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>45523</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>45999</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45782</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>46008</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>46008</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>46009</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>46237</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>45170</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>45554</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>46281</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>46286</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>46037</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>46038</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45797</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>46287</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>46058</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>46059</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>45254</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44886</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         <v>46251</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>46079</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>46176</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>46297</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>46297</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>46297</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>46093</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>46293</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44902</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>45743</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>45847</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>45600</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>45847</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>45554</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>46107</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>45176</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>46111</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>46111</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>46195</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>46174</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20452,7 +20452,7 @@
         <v>46185</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>46114</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>45608</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>46122</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>46013</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>46122</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>46150</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>46176</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>46198</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45882</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>45688</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45789</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>45707</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>44729</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>46134</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>45758</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>46300</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>45727</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>45911</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45754</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45626</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>46309</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45911</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45793</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>45951</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>45804</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>46268</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>46309</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>46266</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>46309</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>46309</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>45825</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>45901</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>46309</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>46266</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>46267</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>46266</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>46267</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>46310</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>44809</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>45544</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>46310</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>46268</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>46311</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45727</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45707</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>46311</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>46269</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>46311</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>46269</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>46311</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>46048</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>46013</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>45553</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24449,7 +24449,7 @@
         <v>46013</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>45600</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>46275</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>46317</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>46275</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24824,7 +24824,7 @@
         <v>46274</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24897,7 +24897,7 @@
         <v>46311</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>46317</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         <v>46274</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25116,7 +25116,7 @@
         <v>44991</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>45320</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>45624</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44895</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>45930</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>45266</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>45288</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>46155</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>46155</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>45348</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>45626</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>46157</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>45113</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>44496</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44991</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>45119</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45608</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>45614</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>44999</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>45189</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26601,7 +26601,7 @@
         <v>45105</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>45700</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>45700</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>44987</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>45552</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>45228</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44861</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>45071</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>44879</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         <v>45247</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>45749</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>45244</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>44924</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>45532</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>44861</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>44586</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>44981</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>45040</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>44904</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>44939</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>44866</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>45544</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>45103</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28295,7 +28295,7 @@
         <v>45111</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>45341</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>45034</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>45093</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44907</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>45624</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>45307</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28806,7 +28806,7 @@
         <v>45114</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>44496</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28952,7 +28952,7 @@
         <v>45386</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>45581</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         <v>45058</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29171,7 +29171,7 @@
         <v>44552</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
         <v>45393</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>45546</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45348</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>44972</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>45360</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>44984</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>45175</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>45614</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>45145</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>44987</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44993</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30062,7 +30062,7 @@
         <v>45162</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>45348</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>45239</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>45204</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>45702</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>44625</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>44625</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>45203</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>45173</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>45194</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45168</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
         <v>45547</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>45638</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45090</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45090</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45160</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>44677</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>45190</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45700</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>45700</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>45093</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>44882</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>45247</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>45145</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>45274</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>45154</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>44760</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32043,7 +32043,7 @@
         <v>45259</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>45306</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>44559</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v>45244</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>45547</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32418,7 +32418,7 @@
         <v>45329</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32491,7 +32491,7 @@
         <v>44861</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>45093</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>44592</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>44592</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32783,7 +32783,7 @@
         <v>44966</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>44788</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>45524</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33007,7 +33007,7 @@
         <v>44903</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>44966</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>44966</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>45140</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>45140</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>45636</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>45835</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>44958</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33591,7 +33591,7 @@
         <v>44958</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33664,7 +33664,7 @@
         <v>45938</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>46125</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33810,7 +33810,7 @@
         <v>46155</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>46155</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>46198</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         <v>46199</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>46198</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>46198</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>46203</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>46251</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>46297</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>

--- a/Översikt HÖGSBY.xlsx
+++ b/Översikt HÖGSBY.xlsx
@@ -601,7 +601,7 @@
         <v>46111</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45611</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46111</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>44559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45224</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>46281</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>44867</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>46199</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>44679</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>45636</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>44866</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>45268</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>45345</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44886</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>45783</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>45626</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>44895</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>46184</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45982</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>46122</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>44853</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>45230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>45076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>46307</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>45359</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>45202</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>45352</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>46111</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>45268</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>46184</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>46184</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>45268</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46244</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>46051</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>45268</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>44617</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>45110</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>44985</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>44504</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>45256</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>46167</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>46181</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>46184</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>46199</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>46206</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>46212</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>46289</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>46251</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>46129</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>46134</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45883</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>45546</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>46157</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>45085</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>45547</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>44868</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>44903</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>44907</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>45145</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>44573</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>45145</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>45770</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44650</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>44602</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>44958</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>45749</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>45761</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>44958</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>46111</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>44501</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>44831</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>44851</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>44585</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>44559</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>44568</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>44603</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>44609</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>44559</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>44579</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44686</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>44644</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>44593</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>44818</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>44551</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>44539</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>44719</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>44880</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>44698</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>44607</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>44542</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>44542</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>44503</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>44601</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>44876</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>44634</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>44543</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>44613</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>44953</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>45838</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>44601</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>45546</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>45447</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>46162</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45222</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>45015</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>44903</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>46167</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45775</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>45222</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>45217</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>45365</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45222</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>44725</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>46169</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>44876</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>44981</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>45183</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>45460</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>45391</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>44950</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>45189</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>45393</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>45946</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>45946</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>44809</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>46181</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>45946</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>45950</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>46181</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>45953</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>46184</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>46184</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>45954</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>46184</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>46184</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>45954</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>46184</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>45012</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>46184</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45126</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>46188</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>45268</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>44866</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>44981</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>46191</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>45588</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45966</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>45692</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>46197</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>46197</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>46196</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>45974</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>45239</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>45337</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>46198</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>46198</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>46198</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>46199</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>45001</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>46198</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>46199</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>46198</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>45279</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>46198</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>46198</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>46202</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>45153</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>45979</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>44623</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>45469</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>44879</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>45103</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>44907</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>45203</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>45203</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44966</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>46206</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>46206</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>46206</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>46206</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>46206</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>45988</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>45994</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>45622</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>45320</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>45414</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>45999</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45999</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>45999</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>46001</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>45999</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>45523</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>45999</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45782</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>46008</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>46008</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>46009</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>46237</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>45170</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>45554</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>46281</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>46286</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>46037</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>46038</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45797</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>46287</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>46058</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>46059</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>45254</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44886</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         <v>46251</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>46079</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>46176</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>46297</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>46297</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>46297</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>46093</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>46293</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44902</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>45743</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>45847</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>45600</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>45847</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>45554</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>46107</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>45176</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>46111</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>46111</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>46195</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>46174</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20452,7 +20452,7 @@
         <v>46185</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>46114</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>45608</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>46122</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>46013</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>46122</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>46150</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>46176</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>46198</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45882</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>45688</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45789</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>45707</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>44729</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>46134</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>45758</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>46300</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>45727</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>45911</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45754</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45626</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>46309</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45911</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45793</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>45951</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>45804</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>46268</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>46309</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>46266</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>46309</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>46309</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>45825</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>45901</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>46309</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>46266</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>46267</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>46266</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>46267</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>46310</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>44809</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>45544</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>46310</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>46268</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>46311</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45727</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45707</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>46311</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>46269</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>46311</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>46269</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>46311</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>46048</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>46013</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>45553</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24449,7 +24449,7 @@
         <v>46013</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>45600</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>46275</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>46317</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>46275</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24824,7 +24824,7 @@
         <v>46274</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24897,7 +24897,7 @@
         <v>46311</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>46317</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         <v>46274</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25116,7 +25116,7 @@
         <v>44991</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>45320</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>45624</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44895</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>45930</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>45266</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>45288</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>46155</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>46155</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>45348</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>45626</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>46157</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>45113</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>44496</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44991</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>45119</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45608</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>45614</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>44999</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>45189</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26601,7 +26601,7 @@
         <v>45105</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>45700</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>45700</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>44987</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>45552</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>45228</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44861</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>45071</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>44879</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         <v>45247</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>45749</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>45244</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>44924</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>45532</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>44861</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>44586</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>44981</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>45040</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>44904</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>44939</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>44866</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>45544</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>45103</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28295,7 +28295,7 @@
         <v>45111</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>45341</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>45034</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>45093</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44907</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>45624</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>45307</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28806,7 +28806,7 @@
         <v>45114</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>44496</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28952,7 +28952,7 @@
         <v>45386</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>45581</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         <v>45058</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29171,7 +29171,7 @@
         <v>44552</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
         <v>45393</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>45546</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45348</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>44972</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>45360</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>44984</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>45175</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>45614</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>45145</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>44987</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44993</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30062,7 +30062,7 @@
         <v>45162</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>45348</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>45239</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>45204</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>45702</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>44625</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>44625</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>45203</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>45173</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>45194</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45168</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
         <v>45547</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>45638</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45090</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45090</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45160</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>44677</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>45190</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45700</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>45700</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>45093</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>44882</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>45247</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>45145</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>45274</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>45154</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>44760</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32043,7 +32043,7 @@
         <v>45259</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>45306</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>44559</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v>45244</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>45547</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32418,7 +32418,7 @@
         <v>45329</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32491,7 +32491,7 @@
         <v>44861</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>45093</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>44592</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>44592</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32783,7 +32783,7 @@
         <v>44966</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>44788</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>45524</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33007,7 +33007,7 @@
         <v>44903</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>44966</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>44966</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>45140</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>45140</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>45636</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>45835</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>44958</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33591,7 +33591,7 @@
         <v>44958</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33664,7 +33664,7 @@
         <v>45938</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>46125</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33810,7 +33810,7 @@
         <v>46155</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>46155</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>46198</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         <v>46199</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>46198</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>46198</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>46203</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>46251</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>46297</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
